--- a/data/playground copy.xlsx
+++ b/data/playground copy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Management - Checklist" sheetId="1" state="visible" r:id="rId1"/>
@@ -2110,216 +2110,213 @@
     <xf numFmtId="165" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="21" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="22" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="22" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="23" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="24" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="24" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="21" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="25" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="22" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="22" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="23" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="24" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="26" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="24" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="25" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="26" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2361,6 +2358,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="19" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -3099,7 +3099,7 @@
       <c r="K6" s="159" t="n"/>
       <c r="L6" s="159" t="n"/>
     </row>
-    <row r="7" hidden="1" ht="17.25" customHeight="1">
+    <row r="7" hidden="1" ht="18.75" customHeight="1">
       <c r="A7" s="331" t="inlineStr">
         <is>
           <t>Print + Post Comp Tree / Tableau Dashboard</t>
@@ -3117,7 +3117,7 @@
       <c r="K7" s="159" t="n"/>
       <c r="L7" s="159" t="n"/>
     </row>
-    <row r="8" hidden="1" ht="17.25" customHeight="1">
+    <row r="8" hidden="1" ht="18.75" customHeight="1">
       <c r="A8" s="331" t="inlineStr">
         <is>
           <t>Update Workbook 2.0 On Previous Day Results</t>
@@ -3279,7 +3279,7 @@
       <c r="K16" s="159" t="n"/>
       <c r="L16" s="159" t="n"/>
     </row>
-    <row r="17" hidden="1" ht="17.25" customHeight="1">
+    <row r="17" hidden="1" ht="18.75" customHeight="1">
       <c r="A17" s="331" t="inlineStr">
         <is>
           <t>Manager Sign Off On Stylist Opening Checklist</t>
@@ -3344,7 +3344,7 @@
       <c r="K18" s="159" t="n"/>
       <c r="L18" s="159" t="n"/>
     </row>
-    <row r="19" hidden="1" ht="17.25" customHeight="1">
+    <row r="19" hidden="1" ht="18.75" customHeight="1">
       <c r="A19" s="331" t="inlineStr">
         <is>
           <t>Complete Daily Damages &amp; Defectives</t>
@@ -3481,7 +3481,7 @@
       <c r="K24" s="159" t="n"/>
       <c r="L24" s="159" t="n"/>
     </row>
-    <row r="25" hidden="1" ht="17.25" customHeight="1">
+    <row r="25" hidden="1" ht="18.75" customHeight="1">
       <c r="A25" s="321" t="inlineStr">
         <is>
           <t>Morning Sanitize High Touch Surfaces 
@@ -3500,7 +3500,7 @@
       <c r="K25" s="159" t="n"/>
       <c r="L25" s="159" t="n"/>
     </row>
-    <row r="26" hidden="1" ht="17.25" customHeight="1">
+    <row r="26" hidden="1" ht="18.75" customHeight="1">
       <c r="A26" s="321" t="inlineStr">
         <is>
           <t>Mid Day Sanitize High Touch Surfaces 
@@ -3556,7 +3556,7 @@
       <c r="K28" s="159" t="n"/>
       <c r="L28" s="159" t="n"/>
     </row>
-    <row r="29" hidden="1" ht="17.25" customHeight="1">
+    <row r="29" hidden="1" ht="18.75" customHeight="1">
       <c r="A29" s="323" t="inlineStr">
         <is>
           <t>Complete Front Door Sensormatic Alarm Check</t>
@@ -3739,7 +3739,7 @@
       <c r="K38" s="159" t="n"/>
       <c r="L38" s="159" t="n"/>
     </row>
-    <row r="39" hidden="1" ht="17.25" customHeight="1">
+    <row r="39" hidden="1" ht="18.75" customHeight="1">
       <c r="A39" s="331" t="inlineStr">
         <is>
           <t>Manager Sign Off On Stylist Closing Checklist</t>
@@ -4121,7 +4121,7 @@
       <c r="K53" s="159" t="n"/>
       <c r="L53" s="159" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="17.25" customHeight="1">
+    <row r="54" hidden="1" ht="18.75" customHeight="1">
       <c r="A54" s="331" t="inlineStr">
         <is>
           <t>Complete Staples Order Audit Checklist (Every Week)</t>
@@ -4875,7 +4875,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="164" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="164" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="195" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="195" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="90.75" customHeight="1">
@@ -5792,7 +5792,7 @@
       <c r="W20" s="89" t="n"/>
       <c r="X20" s="56" t="n"/>
     </row>
-    <row r="21" hidden="1" ht="17.25" customHeight="1">
+    <row r="21" hidden="1" ht="18.75" customHeight="1">
       <c r="A21" s="94" t="n"/>
       <c r="B21" s="95">
         <f>B15+#REF!</f>
@@ -5825,7 +5825,7 @@
       <c r="W21" s="89" t="n"/>
       <c r="X21" s="56" t="n"/>
     </row>
-    <row r="22" hidden="1" ht="17.25" customHeight="1">
+    <row r="22" hidden="1" ht="18.75" customHeight="1">
       <c r="A22" s="100" t="n"/>
       <c r="B22" s="101" t="n">
         <v>1</v>
@@ -7146,7 +7146,7 @@
       <c r="W59" s="151" t="n"/>
       <c r="X59" s="134" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="17.25" customHeight="1">
+    <row r="60" hidden="1" ht="18.75" customHeight="1">
       <c r="A60" s="159" t="n"/>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="124" t="n"/>
@@ -7359,7 +7359,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="165" min="17" max="17"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="165" min="18" max="18"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="19" max="19"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="20" max="20"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="20" max="20"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="159" min="21" max="21"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="159" min="22" max="22"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="159" min="23" max="23"/>
@@ -7986,7 +7986,7 @@
       <c r="W16" s="159" t="n"/>
       <c r="X16" s="159" t="n"/>
     </row>
-    <row r="17" ht="21" customHeight="1">
+    <row r="17" ht="20.25" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
           <t>% TO MONTH SALES PLAN</t>
@@ -8055,7 +8055,7 @@
       <c r="W17" s="159" t="n"/>
       <c r="X17" s="159" t="n"/>
     </row>
-    <row r="18" ht="38.25" customHeight="1">
+    <row r="18" ht="39" customHeight="1">
       <c r="A18" s="30" t="n"/>
       <c r="B18" s="80" t="n"/>
       <c r="C18" s="3" t="n"/>
@@ -8099,7 +8099,7 @@
       <c r="W18" s="159" t="n"/>
       <c r="X18" s="159" t="n"/>
     </row>
-    <row r="19" ht="38.25" customHeight="1">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="30" t="n"/>
       <c r="B19" s="80" t="n"/>
       <c r="C19" s="3" t="n"/>
@@ -8151,7 +8151,7 @@
       <c r="W19" s="159" t="n"/>
       <c r="X19" s="159" t="n"/>
     </row>
-    <row r="20" ht="38.25" customHeight="1">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="30" t="n"/>
       <c r="B20" s="80" t="n"/>
       <c r="C20" s="3" t="n"/>
@@ -8197,7 +8197,7 @@
       <c r="W20" s="159" t="n"/>
       <c r="X20" s="159" t="n"/>
     </row>
-    <row r="21" ht="38.25" customHeight="1">
+    <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="94" t="n"/>
       <c r="B21" s="95">
         <f>B15+#REF!</f>
@@ -8246,7 +8246,7 @@
       <c r="W21" s="159" t="n"/>
       <c r="X21" s="159" t="n"/>
     </row>
-    <row r="22" ht="38.25" customHeight="1">
+    <row r="22" ht="23.25" customHeight="1">
       <c r="A22" s="100" t="n"/>
       <c r="B22" s="101" t="n">
         <v>1</v>
@@ -8295,7 +8295,7 @@
       <c r="W22" s="159" t="n"/>
       <c r="X22" s="159" t="n"/>
     </row>
-    <row r="23" ht="38.25" customHeight="1">
+    <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="100" t="n"/>
       <c r="B23" s="103" t="n"/>
       <c r="C23" s="3" t="n"/>
@@ -8341,7 +8341,7 @@
       <c r="W23" s="159" t="n"/>
       <c r="X23" s="159" t="n"/>
     </row>
-    <row r="24" ht="38.25" customHeight="1">
+    <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="100" t="n"/>
       <c r="B24" s="103" t="n"/>
       <c r="C24" s="3" t="n"/>
@@ -8391,7 +8391,7 @@
       <c r="W24" s="159" t="n"/>
       <c r="X24" s="159" t="n"/>
     </row>
-    <row r="25" ht="27.75" customHeight="1">
+    <row r="25" ht="30.75" customHeight="1">
       <c r="A25" s="106" t="inlineStr">
         <is>
           <t>DENIM: 69.99 when you buy 2 or more</t>
@@ -8440,7 +8440,7 @@
       <c r="W25" s="159" t="n"/>
       <c r="X25" s="159" t="n"/>
     </row>
-    <row r="26" ht="27.75" customHeight="1">
+    <row r="26" ht="30.75" customHeight="1">
       <c r="A26" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">TOPS, OUTERWEAR, SHORTS: BOGO 50% </t>
@@ -8491,7 +8491,7 @@
       <c r="W26" s="159" t="n"/>
       <c r="X26" s="159" t="n"/>
     </row>
-    <row r="27" ht="27.75" customHeight="1">
+    <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="112" t="inlineStr">
         <is>
           <t>40 % off CLEARANCE</t>
@@ -8543,7 +8543,7 @@
       <c r="W27" s="159" t="n"/>
       <c r="X27" s="159" t="n"/>
     </row>
-    <row r="28" ht="27.75" customHeight="1">
+    <row r="28" ht="30.75" customHeight="1">
       <c r="A28" s="159" t="n"/>
       <c r="B28" s="113" t="n"/>
       <c r="C28" s="3" t="n"/>
@@ -8591,7 +8591,7 @@
       <c r="W28" s="159" t="n"/>
       <c r="X28" s="159" t="n"/>
     </row>
-    <row r="29" ht="27.75" customHeight="1">
+    <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="117" t="inlineStr">
         <is>
           <t>SW. $34.99, $39.99, 44.99, 49.99</t>
@@ -8643,7 +8643,7 @@
       <c r="W29" s="159" t="n"/>
       <c r="X29" s="159" t="n"/>
     </row>
-    <row r="30" ht="27.75" customHeight="1">
+    <row r="30" ht="23.25" customHeight="1">
       <c r="A30" s="117" t="n"/>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="3" t="n"/>
@@ -8691,7 +8691,7 @@
       <c r="W30" s="159" t="n"/>
       <c r="X30" s="159" t="n"/>
     </row>
-    <row r="31" ht="27.75" customHeight="1">
+    <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="120" t="n"/>
       <c r="B31" s="121" t="n"/>
       <c r="C31" s="3" t="n"/>
@@ -10187,20 +10187,20 @@
     <col width="29.005" bestFit="1" customWidth="1" style="159" min="8" max="8"/>
     <col width="21.005" bestFit="1" customWidth="1" style="162" min="9" max="9"/>
     <col width="16.29071428571428" bestFit="1" customWidth="1" style="294" min="10" max="10"/>
-    <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="11" max="11"/>
+    <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="11" max="11"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="12" max="12"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="13" max="13"/>
-    <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="14" max="14"/>
+    <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="14" max="14"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="15" max="15"/>
-    <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="16" max="16"/>
-    <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="17" max="17"/>
+    <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="16" max="16"/>
+    <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="17" max="17"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="18" max="18"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="19" max="19"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="20" max="20"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="295" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
@@ -10248,7 +10248,7 @@
       <c r="W2" s="362" t="n"/>
       <c r="X2" s="19" t="n"/>
     </row>
-    <row r="3" ht="20.25" customHeight="1">
+    <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
           <t>DATE</t>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="I3" s="362" t="n"/>
       <c r="J3" s="197" t="n"/>
-      <c r="K3" s="25" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t>9am - 10am</t>
         </is>
@@ -10286,7 +10286,7 @@
           <t>11am - 12pm</t>
         </is>
       </c>
-      <c r="N3" s="25" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t>12pm - 1pm</t>
         </is>
@@ -10296,12 +10296,12 @@
           <t>1pm - 2pm</t>
         </is>
       </c>
-      <c r="P3" s="25" t="inlineStr">
+      <c r="P3" s="24" t="inlineStr">
         <is>
           <t>2pm - 3pm</t>
         </is>
       </c>
-      <c r="Q3" s="25" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t>3pm - 4pm</t>
         </is>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="X3" s="19" t="n"/>
     </row>
-    <row r="4" ht="33.75" customHeight="1">
+    <row r="4" ht="33" customHeight="1">
       <c r="A4" s="30" t="inlineStr">
         <is>
           <t>DAY SALES TARGET</t>
@@ -10838,7 +10838,7 @@
       <c r="C15" s="3" t="n"/>
       <c r="H15" s="159" t="n"/>
       <c r="I15" s="64" t="n"/>
-      <c r="J15" s="284" t="n"/>
+      <c r="J15" s="283" t="n"/>
       <c r="K15" s="68" t="n"/>
       <c r="L15" s="68" t="n"/>
       <c r="M15" s="68" t="n"/>
@@ -10902,7 +10902,7 @@
           <t>Shift</t>
         </is>
       </c>
-      <c r="J17" s="286" t="inlineStr">
+      <c r="J17" s="285" t="inlineStr">
         <is>
           <t>8am-9am</t>
         </is>
@@ -10968,7 +10968,7 @@
           <t>MONTH TO GO</t>
         </is>
       </c>
-      <c r="B18" s="287" t="n"/>
+      <c r="B18" s="286" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="H18" s="98" t="inlineStr">
         <is>
@@ -10980,30 +10980,20 @@
           <t>10:00 - 02:45</t>
         </is>
       </c>
-      <c r="J18" s="215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="J18" s="211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="O18" s="49" t="n">
         <v>1</v>
@@ -11022,7 +11012,7 @@
       <c r="W18" s="89" t="n"/>
       <c r="X18" s="56" t="n"/>
     </row>
-    <row r="19" ht="39" customHeight="1">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="30" t="n"/>
       <c r="B19" s="80" t="n"/>
       <c r="C19" s="3" t="n"/>
@@ -11040,45 +11030,29 @@
           <t>10:00 - 06:30</t>
         </is>
       </c>
-      <c r="J19" s="215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q19" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="J19" s="211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="R19" s="49" t="n"/>
       <c r="S19" s="45" t="n"/>
@@ -11088,7 +11062,7 @@
       <c r="W19" s="89" t="n"/>
       <c r="X19" s="56" t="n"/>
     </row>
-    <row r="20" ht="39" customHeight="1">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="30" t="n"/>
       <c r="B20" s="80" t="n"/>
       <c r="C20" s="3" t="n"/>
@@ -11106,38 +11080,28 @@
           <t>10:00 - 02:45</t>
         </is>
       </c>
-      <c r="J20" s="215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L20" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" s="288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N20" s="289" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O20" s="289" t="n">
+      <c r="J20" s="211" t="n">
         <v>1</v>
       </c>
-      <c r="P20" s="289" t="n">
+      <c r="K20" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" s="289" t="n">
+      <c r="L20" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="287" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="288" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="288" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="288" t="n">
         <v>1</v>
       </c>
       <c r="R20" s="45" t="n">
@@ -11154,7 +11118,7 @@
     </row>
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="94" t="n"/>
-      <c r="B21" s="257">
+      <c r="B21" s="246">
         <f>B15+B18</f>
         <v/>
       </c>
@@ -11173,31 +11137,21 @@
           <t>11:15 - 04:00</t>
         </is>
       </c>
-      <c r="J21" s="215" t="n"/>
-      <c r="K21" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N21" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O21" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="J21" s="211" t="n"/>
+      <c r="K21" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="P21" s="45" t="n">
         <v>1</v>
@@ -11237,31 +11191,21 @@
           <t>11:15 - 04:00</t>
         </is>
       </c>
-      <c r="J22" s="215" t="n"/>
-      <c r="K22" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O22" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="J22" s="211" t="n"/>
+      <c r="K22" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="P22" s="45" t="n">
         <v>1</v>
@@ -11295,31 +11239,21 @@
           <t>11:15 - 04:00</t>
         </is>
       </c>
-      <c r="J23" s="215" t="n"/>
-      <c r="K23" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N23" s="49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O23" s="104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="J23" s="211" t="n"/>
+      <c r="K23" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="104" t="n">
+        <v>1</v>
       </c>
       <c r="P23" s="104" t="n">
         <v>1</v>
@@ -11358,37 +11292,25 @@
           <t>12:15 - 06:30</t>
         </is>
       </c>
-      <c r="J24" s="215" t="n"/>
+      <c r="J24" s="211" t="n"/>
       <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N24" s="91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O24" s="93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P24" s="92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q24" s="92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="L24" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="92" t="n">
+        <v>1</v>
       </c>
       <c r="R24" s="92" t="n">
         <v>1</v>
@@ -11429,32 +11351,22 @@
           <t>12:15 - 05:00</t>
         </is>
       </c>
-      <c r="J25" s="215" t="n"/>
+      <c r="J25" s="211" t="n"/>
       <c r="K25" s="45" t="n"/>
-      <c r="L25" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O25" s="109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P25" s="109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="L25" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="109" t="n">
+        <v>1</v>
       </c>
       <c r="Q25" s="109" t="n">
         <v>1</v>
@@ -11495,33 +11407,23 @@
           <t>01:15 - 06:00</t>
         </is>
       </c>
-      <c r="J26" s="215" t="n"/>
+      <c r="J26" s="211" t="n"/>
       <c r="K26" s="45" t="n"/>
       <c r="L26" s="45" t="n"/>
-      <c r="M26" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N26" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O26" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P26" s="92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q26" s="93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M26" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="93" t="n">
+        <v>1</v>
       </c>
       <c r="R26" s="93" t="n">
         <v>1</v>
@@ -11538,7 +11440,7 @@
       <c r="V26" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="W26" s="290" t="n"/>
+      <c r="W26" s="289" t="n"/>
       <c r="X26" s="56" t="n"/>
     </row>
     <row r="27" ht="39" customHeight="1">
@@ -11563,38 +11465,28 @@
           <t>01:15 - 06:00</t>
         </is>
       </c>
-      <c r="J27" s="215" t="n"/>
+      <c r="J27" s="211" t="n"/>
       <c r="K27" s="45" t="n"/>
       <c r="L27" s="45" t="n"/>
-      <c r="M27" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N27" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O27" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P27" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q27" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M27" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="R27" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="S27" s="291" t="n">
+      <c r="S27" s="290" t="n">
         <v>1</v>
       </c>
       <c r="T27" s="104" t="n">
@@ -11610,7 +11502,7 @@
       <c r="X27" s="56" t="n"/>
     </row>
     <row r="28" ht="39" customHeight="1">
-      <c r="A28" s="279" t="n"/>
+      <c r="A28" s="278" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="96" t="n"/>
       <c r="E28" s="96" t="n"/>
@@ -11626,33 +11518,23 @@
           <t>01:45 - 06:30</t>
         </is>
       </c>
-      <c r="J28" s="215" t="n"/>
+      <c r="J28" s="211" t="n"/>
       <c r="K28" s="45" t="n"/>
       <c r="L28" s="45" t="n"/>
-      <c r="M28" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N28" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O28" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P28" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q28" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M28" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="R28" s="49" t="n">
         <v>1</v>
@@ -11673,7 +11555,7 @@
       <c r="X28" s="56" t="n"/>
     </row>
     <row r="29" ht="39" customHeight="1">
-      <c r="A29" s="292" t="n"/>
+      <c r="A29" s="291" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="96" t="n"/>
       <c r="E29" s="96" t="n"/>
@@ -11689,33 +11571,23 @@
           <t>01:45 - 06:30</t>
         </is>
       </c>
-      <c r="J29" s="215" t="n"/>
+      <c r="J29" s="211" t="n"/>
       <c r="K29" s="45" t="n"/>
       <c r="L29" s="45" t="n"/>
-      <c r="M29" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N29" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O29" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P29" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q29" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M29" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="R29" s="115" t="n">
         <v>1</v>
@@ -11753,47 +11625,37 @@
           <t>01:45 - 06:30</t>
         </is>
       </c>
-      <c r="J30" s="215" t="n"/>
+      <c r="J30" s="211" t="n"/>
       <c r="K30" s="45" t="n"/>
       <c r="L30" s="45" t="n"/>
-      <c r="M30" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N30" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O30" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P30" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q30" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="R30" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="S30" s="241" t="n">
+      <c r="S30" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="241" t="n">
+      <c r="T30" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="U30" s="241" t="n">
+      <c r="U30" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="V30" s="241" t="n">
+      <c r="V30" s="231" t="n">
         <v>1</v>
       </c>
       <c r="W30" s="189" t="n"/>
@@ -11817,39 +11679,29 @@
           <t>01:45 - 06:30</t>
         </is>
       </c>
-      <c r="J31" s="215" t="n"/>
+      <c r="J31" s="211" t="n"/>
       <c r="K31" s="45" t="n"/>
       <c r="L31" s="45" t="n"/>
-      <c r="M31" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N31" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O31" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P31" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q31" s="45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M31" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="R31" s="49" t="n"/>
-      <c r="S31" s="241" t="n"/>
-      <c r="T31" s="241" t="n"/>
-      <c r="U31" s="241" t="n"/>
-      <c r="V31" s="241" t="n"/>
+      <c r="S31" s="231" t="n"/>
+      <c r="T31" s="231" t="n"/>
+      <c r="U31" s="231" t="n"/>
+      <c r="V31" s="231" t="n"/>
       <c r="W31" s="189" t="n"/>
       <c r="X31" s="127" t="n"/>
     </row>
@@ -11863,7 +11715,7 @@
       <c r="G32" s="97" t="n"/>
       <c r="H32" s="98" t="n"/>
       <c r="I32" s="129" t="n"/>
-      <c r="J32" s="215" t="n"/>
+      <c r="J32" s="211" t="n"/>
       <c r="K32" s="45" t="n"/>
       <c r="L32" s="45" t="n"/>
       <c r="M32" s="45" t="n"/>
@@ -11889,7 +11741,7 @@
       <c r="G33" s="97" t="n"/>
       <c r="H33" s="98" t="n"/>
       <c r="I33" s="129" t="n"/>
-      <c r="J33" s="215" t="n"/>
+      <c r="J33" s="211" t="n"/>
       <c r="K33" s="45" t="n"/>
       <c r="L33" s="45" t="n"/>
       <c r="M33" s="45" t="n"/>
@@ -11915,7 +11767,7 @@
       <c r="G34" s="97" t="n"/>
       <c r="H34" s="98" t="n"/>
       <c r="I34" s="129" t="n"/>
-      <c r="J34" s="215" t="n"/>
+      <c r="J34" s="211" t="n"/>
       <c r="K34" s="45" t="n"/>
       <c r="L34" s="45" t="n"/>
       <c r="M34" s="45" t="n"/>
@@ -11948,7 +11800,7 @@
       <c r="G35" s="97" t="n"/>
       <c r="H35" s="98" t="n"/>
       <c r="I35" s="129" t="n"/>
-      <c r="J35" s="215" t="n"/>
+      <c r="J35" s="211" t="n"/>
       <c r="K35" s="45" t="n"/>
       <c r="L35" s="45" t="n"/>
       <c r="M35" s="45" t="n"/>
@@ -11977,7 +11829,7 @@
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="98" t="n"/>
       <c r="I36" s="129" t="n"/>
-      <c r="J36" s="215" t="n"/>
+      <c r="J36" s="211" t="n"/>
       <c r="K36" s="45" t="n"/>
       <c r="L36" s="45" t="n"/>
       <c r="M36" s="45" t="n"/>
@@ -12006,7 +11858,7 @@
       <c r="G37" s="97" t="n"/>
       <c r="H37" s="132" t="n"/>
       <c r="I37" s="129" t="n"/>
-      <c r="J37" s="215" t="n"/>
+      <c r="J37" s="211" t="n"/>
       <c r="K37" s="45" t="n"/>
       <c r="L37" s="45" t="n"/>
       <c r="M37" s="45" t="n"/>
@@ -12039,7 +11891,7 @@
       <c r="G38" s="97" t="n"/>
       <c r="H38" s="135" t="n"/>
       <c r="I38" s="136" t="n"/>
-      <c r="J38" s="215" t="n"/>
+      <c r="J38" s="211" t="n"/>
       <c r="K38" s="45" t="n"/>
       <c r="L38" s="45" t="n"/>
       <c r="M38" s="45" t="n"/>
@@ -12068,7 +11920,7 @@
       <c r="G39" s="97" t="n"/>
       <c r="H39" s="135" t="n"/>
       <c r="I39" s="137" t="n"/>
-      <c r="J39" s="215" t="n"/>
+      <c r="J39" s="211" t="n"/>
       <c r="K39" s="45" t="n"/>
       <c r="L39" s="45" t="n"/>
       <c r="M39" s="45" t="n"/>
@@ -12097,7 +11949,7 @@
       <c r="G40" s="97" t="n"/>
       <c r="H40" s="135" t="n"/>
       <c r="I40" s="137" t="n"/>
-      <c r="J40" s="215" t="n"/>
+      <c r="J40" s="211" t="n"/>
       <c r="K40" s="45" t="n"/>
       <c r="L40" s="45" t="n"/>
       <c r="M40" s="45" t="n"/>
@@ -12130,7 +11982,7 @@
       <c r="G41" s="97" t="n"/>
       <c r="H41" s="159" t="n"/>
       <c r="I41" s="137" t="n"/>
-      <c r="J41" s="215" t="n"/>
+      <c r="J41" s="211" t="n"/>
       <c r="K41" s="45" t="n"/>
       <c r="L41" s="45" t="n"/>
       <c r="M41" s="45" t="n"/>
@@ -12163,7 +12015,7 @@
           <t>SELECT</t>
         </is>
       </c>
-      <c r="J42" s="215" t="n"/>
+      <c r="J42" s="211" t="n"/>
       <c r="K42" s="45" t="n"/>
       <c r="L42" s="45" t="n"/>
       <c r="M42" s="45" t="n"/>
@@ -12192,7 +12044,7 @@
       <c r="G43" s="97" t="n"/>
       <c r="H43" s="159" t="n"/>
       <c r="I43" s="64" t="n"/>
-      <c r="J43" s="215" t="n"/>
+      <c r="J43" s="211" t="n"/>
       <c r="K43" s="45" t="n"/>
       <c r="L43" s="45" t="n"/>
       <c r="M43" s="45" t="n"/>
@@ -12225,7 +12077,7 @@
       <c r="G44" s="97" t="n"/>
       <c r="H44" s="159" t="n"/>
       <c r="I44" s="64" t="n"/>
-      <c r="J44" s="215" t="n"/>
+      <c r="J44" s="211" t="n"/>
       <c r="K44" s="45" t="n"/>
       <c r="L44" s="45" t="n"/>
       <c r="M44" s="45" t="n"/>
@@ -12254,7 +12106,7 @@
       <c r="G45" s="97" t="n"/>
       <c r="H45" s="159" t="n"/>
       <c r="I45" s="64" t="n"/>
-      <c r="J45" s="215" t="n"/>
+      <c r="J45" s="211" t="n"/>
       <c r="K45" s="45" t="n"/>
       <c r="L45" s="45" t="n"/>
       <c r="M45" s="45" t="n"/>
@@ -12283,7 +12135,7 @@
       <c r="G46" s="97" t="n"/>
       <c r="H46" s="159" t="n"/>
       <c r="I46" s="64" t="n"/>
-      <c r="J46" s="215" t="n"/>
+      <c r="J46" s="211" t="n"/>
       <c r="K46" s="45" t="n"/>
       <c r="L46" s="45" t="n"/>
       <c r="M46" s="45" t="n"/>
@@ -12316,7 +12168,7 @@
       <c r="G47" s="97" t="n"/>
       <c r="H47" s="159" t="n"/>
       <c r="I47" s="64" t="n"/>
-      <c r="J47" s="215" t="n"/>
+      <c r="J47" s="211" t="n"/>
       <c r="K47" s="45" t="n"/>
       <c r="L47" s="45" t="n"/>
       <c r="M47" s="45" t="n"/>
@@ -12349,7 +12201,7 @@
       <c r="G48" s="97" t="n"/>
       <c r="H48" s="159" t="n"/>
       <c r="I48" s="64" t="n"/>
-      <c r="J48" s="215" t="n"/>
+      <c r="J48" s="211" t="n"/>
       <c r="K48" s="45" t="n"/>
       <c r="L48" s="45" t="n"/>
       <c r="M48" s="45" t="n"/>
@@ -12524,7 +12376,7 @@
       <c r="H54" s="159" t="n"/>
       <c r="I54" s="64" t="n"/>
       <c r="J54" s="137" t="n"/>
-      <c r="K54" s="191" t="inlineStr">
+      <c r="K54" s="292" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
@@ -12539,7 +12391,7 @@
           <t>MENS</t>
         </is>
       </c>
-      <c r="N54" s="153" t="inlineStr">
+      <c r="N54" s="154" t="inlineStr">
         <is>
           <t>WOMENS</t>
         </is>
@@ -12549,12 +12401,12 @@
           <t>FLEX</t>
         </is>
       </c>
-      <c r="P54" s="153" t="inlineStr">
+      <c r="P54" s="154" t="inlineStr">
         <is>
           <t>STYLIST</t>
         </is>
       </c>
-      <c r="Q54" s="193" t="inlineStr">
+      <c r="Q54" s="155" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -12597,7 +12449,7 @@
       <c r="G55" s="97" t="n"/>
       <c r="H55" s="159" t="n"/>
       <c r="I55" s="64" t="n"/>
-      <c r="J55" s="284" t="n"/>
+      <c r="J55" s="283" t="n"/>
       <c r="K55" s="68" t="n"/>
       <c r="L55" s="68" t="n"/>
       <c r="M55" s="68" t="n"/>
@@ -12623,7 +12475,7 @@
       <c r="G56" s="147" t="n"/>
       <c r="H56" s="159" t="n"/>
       <c r="I56" s="64" t="n"/>
-      <c r="J56" s="284" t="n"/>
+      <c r="J56" s="283" t="n"/>
       <c r="K56" s="68" t="n"/>
       <c r="L56" s="68" t="n"/>
       <c r="M56" s="68" t="n"/>
@@ -12649,7 +12501,7 @@
       <c r="G57" s="147" t="n"/>
       <c r="H57" s="159" t="n"/>
       <c r="I57" s="64" t="n"/>
-      <c r="J57" s="284" t="n"/>
+      <c r="J57" s="283" t="n"/>
       <c r="K57" s="68" t="n"/>
       <c r="L57" s="68" t="n"/>
       <c r="M57" s="68" t="n"/>
@@ -12675,7 +12527,7 @@
       <c r="G58" s="147" t="n"/>
       <c r="H58" s="159" t="n"/>
       <c r="I58" s="64" t="n"/>
-      <c r="J58" s="284" t="n"/>
+      <c r="J58" s="283" t="n"/>
       <c r="K58" s="68" t="n"/>
       <c r="L58" s="68" t="n"/>
       <c r="M58" s="68" t="n"/>
@@ -12701,7 +12553,7 @@
       <c r="G59" s="159" t="n"/>
       <c r="H59" s="159" t="n"/>
       <c r="I59" s="64" t="n"/>
-      <c r="J59" s="284" t="n"/>
+      <c r="J59" s="283" t="n"/>
       <c r="K59" s="68" t="n"/>
       <c r="L59" s="68" t="n"/>
       <c r="M59" s="68" t="n"/>
@@ -12806,7 +12658,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="88.5" customHeight="1">
@@ -12829,7 +12681,7 @@
       <c r="B2" s="370" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="159" t="n"/>
-      <c r="E2" s="276" t="n"/>
+      <c r="E2" s="274" t="n"/>
       <c r="F2" s="159" t="n"/>
       <c r="G2" s="159" t="n"/>
       <c r="H2" s="14" t="inlineStr">
@@ -12876,7 +12728,7 @@
         </is>
       </c>
       <c r="I3" s="362" t="n"/>
-      <c r="J3" s="249" t="n"/>
+      <c r="J3" s="238" t="n"/>
       <c r="K3" s="26" t="inlineStr">
         <is>
           <t>9am - 10am</t>
@@ -12963,7 +12815,7 @@
         </is>
       </c>
       <c r="I4" s="368" t="n"/>
-      <c r="J4" s="250" t="n"/>
+      <c r="J4" s="239" t="n"/>
       <c r="K4" s="36" t="n"/>
       <c r="L4" s="36" t="n">
         <v>0.04</v>
@@ -13026,7 +12878,7 @@
         </is>
       </c>
       <c r="I5" s="368" t="n"/>
-      <c r="J5" s="251" t="n"/>
+      <c r="J5" s="240" t="n"/>
       <c r="K5" s="38">
         <f>K4*B4</f>
         <v/>
@@ -13105,7 +12957,7 @@
         </is>
       </c>
       <c r="I6" s="368" t="n"/>
-      <c r="J6" s="251" t="n"/>
+      <c r="J6" s="240" t="n"/>
       <c r="K6" s="38">
         <f>K4*B5</f>
         <v/>
@@ -13176,7 +13028,7 @@
         </is>
       </c>
       <c r="I7" s="368" t="n"/>
-      <c r="J7" s="252" t="n"/>
+      <c r="J7" s="241" t="n"/>
       <c r="K7" s="45" t="n"/>
       <c r="L7" s="45" t="n"/>
       <c r="M7" s="45" t="n"/>
@@ -13223,7 +13075,7 @@
         </is>
       </c>
       <c r="I8" s="368" t="n"/>
-      <c r="J8" s="252" t="n"/>
+      <c r="J8" s="241" t="n"/>
       <c r="K8" s="47" t="n"/>
       <c r="L8" s="47" t="n"/>
       <c r="M8" s="47" t="n"/>
@@ -13255,7 +13107,7 @@
         </is>
       </c>
       <c r="I9" s="368" t="n"/>
-      <c r="J9" s="253" t="n"/>
+      <c r="J9" s="242" t="n"/>
       <c r="K9" s="47" t="n"/>
       <c r="L9" s="47" t="n"/>
       <c r="M9" s="47" t="n"/>
@@ -13287,7 +13139,7 @@
         </is>
       </c>
       <c r="I10" s="368" t="n"/>
-      <c r="J10" s="252" t="n"/>
+      <c r="J10" s="241" t="n"/>
       <c r="K10" s="49" t="n"/>
       <c r="L10" s="49" t="n"/>
       <c r="M10" s="49" t="n"/>
@@ -13319,7 +13171,7 @@
         </is>
       </c>
       <c r="I11" s="368" t="n"/>
-      <c r="J11" s="252" t="n"/>
+      <c r="J11" s="241" t="n"/>
       <c r="K11" s="50" t="n"/>
       <c r="L11" s="50" t="n"/>
       <c r="M11" s="50" t="n"/>
@@ -13351,7 +13203,7 @@
         </is>
       </c>
       <c r="I12" s="368" t="n"/>
-      <c r="J12" s="252" t="n"/>
+      <c r="J12" s="241" t="n"/>
       <c r="K12" s="45" t="n"/>
       <c r="L12" s="45" t="n"/>
       <c r="M12" s="45" t="n"/>
@@ -13383,7 +13235,7 @@
         </is>
       </c>
       <c r="I13" s="368" t="n"/>
-      <c r="J13" s="254" t="n"/>
+      <c r="J13" s="243" t="n"/>
       <c r="K13" s="45" t="n"/>
       <c r="L13" s="45" t="n"/>
       <c r="M13" s="45" t="n"/>
@@ -13413,7 +13265,7 @@
         </is>
       </c>
       <c r="I14" s="372" t="n"/>
-      <c r="J14" s="255" t="n"/>
+      <c r="J14" s="244" t="n"/>
       <c r="K14" s="61" t="n"/>
       <c r="L14" s="61" t="n"/>
       <c r="M14" s="61" t="n"/>
@@ -13579,12 +13431,12 @@
           <t>8-430</t>
         </is>
       </c>
-      <c r="J18" s="210" t="inlineStr">
+      <c r="J18" s="209" t="inlineStr">
         <is>
           <t>TASK</t>
         </is>
       </c>
-      <c r="K18" s="277" t="inlineStr">
+      <c r="K18" s="275" t="inlineStr">
         <is>
           <t>TASK</t>
         </is>
@@ -13641,15 +13493,15 @@
           <t>8-12:45</t>
         </is>
       </c>
-      <c r="J19" s="210" t="inlineStr">
+      <c r="J19" s="209" t="inlineStr">
         <is>
           <t>TASK</t>
         </is>
       </c>
-      <c r="K19" s="278" t="n"/>
-      <c r="L19" s="278" t="n"/>
-      <c r="M19" s="278" t="n"/>
-      <c r="N19" s="278" t="n"/>
+      <c r="K19" s="276" t="n"/>
+      <c r="L19" s="276" t="n"/>
+      <c r="M19" s="276" t="n"/>
+      <c r="N19" s="276" t="n"/>
       <c r="O19" s="45" t="n"/>
       <c r="P19" s="45" t="n"/>
       <c r="Q19" s="45" t="n"/>
@@ -13661,7 +13513,7 @@
       <c r="W19" s="89" t="n"/>
       <c r="X19" s="56" t="n"/>
     </row>
-    <row r="20" hidden="1" ht="17.25" customHeight="1">
+    <row r="20" hidden="1" ht="18.75" customHeight="1">
       <c r="A20" s="94" t="n"/>
       <c r="B20" s="95">
         <f>B15+#REF!</f>
@@ -13682,7 +13534,7 @@
           <t>12-5</t>
         </is>
       </c>
-      <c r="J20" s="215" t="n"/>
+      <c r="J20" s="211" t="n"/>
       <c r="K20" s="45" t="n"/>
       <c r="L20" s="45" t="n"/>
       <c r="M20" s="45" t="n"/>
@@ -13698,7 +13550,7 @@
       <c r="W20" s="89" t="n"/>
       <c r="X20" s="56" t="n"/>
     </row>
-    <row r="21" hidden="1" ht="17.25" customHeight="1">
+    <row r="21" hidden="1" ht="18.75" customHeight="1">
       <c r="A21" s="100" t="n"/>
       <c r="B21" s="101" t="n">
         <v>1</v>
@@ -13710,7 +13562,7 @@
       <c r="G21" s="97" t="n"/>
       <c r="H21" s="98" t="n"/>
       <c r="I21" s="129" t="n"/>
-      <c r="J21" s="215" t="n"/>
+      <c r="J21" s="211" t="n"/>
       <c r="K21" s="45" t="n"/>
       <c r="L21" s="45" t="n"/>
       <c r="M21" s="45" t="n"/>
@@ -13744,7 +13596,7 @@
           <t>10-630</t>
         </is>
       </c>
-      <c r="J22" s="215" t="n"/>
+      <c r="J22" s="211" t="n"/>
       <c r="K22" s="45" t="n"/>
       <c r="L22" s="49" t="inlineStr">
         <is>
@@ -13790,7 +13642,7 @@
       <c r="U22" s="45" t="n"/>
       <c r="V22" s="45" t="n"/>
       <c r="W22" s="89" t="n"/>
-      <c r="X22" s="274" t="n"/>
+      <c r="X22" s="272" t="n"/>
     </row>
     <row r="23" ht="27.75" customHeight="1">
       <c r="A23" s="106" t="inlineStr">
@@ -13813,7 +13665,7 @@
           <t>10-5</t>
         </is>
       </c>
-      <c r="J23" s="215" t="n"/>
+      <c r="J23" s="211" t="n"/>
       <c r="K23" s="45" t="n"/>
       <c r="L23" s="49" t="inlineStr">
         <is>
@@ -13831,7 +13683,7 @@
       <c r="U23" s="45" t="n"/>
       <c r="V23" s="45" t="n"/>
       <c r="W23" s="89" t="n"/>
-      <c r="X23" s="274" t="n"/>
+      <c r="X23" s="272" t="n"/>
     </row>
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="106" t="inlineStr">
@@ -13854,7 +13706,7 @@
           <t>11:15-4</t>
         </is>
       </c>
-      <c r="J24" s="215" t="n"/>
+      <c r="J24" s="211" t="n"/>
       <c r="K24" s="119" t="n"/>
       <c r="L24" s="45" t="n"/>
       <c r="M24" s="49" t="inlineStr">
@@ -13876,7 +13728,7 @@
       <c r="U24" s="45" t="n"/>
       <c r="V24" s="45" t="n"/>
       <c r="W24" s="89" t="n"/>
-      <c r="X24" s="274" t="n"/>
+      <c r="X24" s="272" t="n"/>
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="106" t="inlineStr">
@@ -13899,7 +13751,7 @@
           <t>12:15-5</t>
         </is>
       </c>
-      <c r="J25" s="215" t="n"/>
+      <c r="J25" s="211" t="n"/>
       <c r="K25" s="138" t="n"/>
       <c r="L25" s="45" t="n"/>
       <c r="M25" s="45" t="n"/>
@@ -13933,7 +13785,7 @@
       <c r="U25" s="45" t="n"/>
       <c r="V25" s="45" t="n"/>
       <c r="W25" s="89" t="n"/>
-      <c r="X25" s="274" t="n"/>
+      <c r="X25" s="272" t="n"/>
     </row>
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="117" t="n"/>
@@ -13953,7 +13805,7 @@
           <t>1-930</t>
         </is>
       </c>
-      <c r="J26" s="210" t="n"/>
+      <c r="J26" s="209" t="n"/>
       <c r="K26" s="45" t="n"/>
       <c r="L26" s="45" t="n"/>
       <c r="M26" s="45" t="n"/>
@@ -13968,7 +13820,7 @@
           <t>CEL</t>
         </is>
       </c>
-      <c r="Q26" s="269" t="inlineStr">
+      <c r="Q26" s="277" t="inlineStr">
         <is>
           <t>MENS</t>
         </is>
@@ -13978,7 +13830,7 @@
           <t>MENS</t>
         </is>
       </c>
-      <c r="S26" s="269" t="inlineStr">
+      <c r="S26" s="277" t="inlineStr">
         <is>
           <t>MENS</t>
         </is>
@@ -13999,10 +13851,10 @@
         </is>
       </c>
       <c r="W26" s="89" t="n"/>
-      <c r="X26" s="274" t="n"/>
+      <c r="X26" s="272" t="n"/>
     </row>
     <row r="27" ht="27.75" customHeight="1">
-      <c r="A27" s="279" t="n"/>
+      <c r="A27" s="278" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="96" t="n"/>
       <c r="E27" s="96" t="n"/>
@@ -14018,7 +13870,7 @@
           <t>2:15-7</t>
         </is>
       </c>
-      <c r="J27" s="210" t="n"/>
+      <c r="J27" s="209" t="n"/>
       <c r="K27" s="45" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="45" t="n"/>
@@ -14052,7 +13904,7 @@
       <c r="U27" s="45" t="n"/>
       <c r="V27" s="45" t="n"/>
       <c r="W27" s="89" t="n"/>
-      <c r="X27" s="274" t="n"/>
+      <c r="X27" s="272" t="n"/>
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="186" t="n"/>
@@ -14071,7 +13923,7 @@
           <t>4:45-930</t>
         </is>
       </c>
-      <c r="J28" s="215" t="n"/>
+      <c r="J28" s="211" t="n"/>
       <c r="K28" s="45" t="n"/>
       <c r="L28" s="45" t="n"/>
       <c r="M28" s="45" t="n"/>
@@ -14088,7 +13940,7 @@
       <c r="T28" s="108" t="n"/>
       <c r="U28" s="108" t="n"/>
       <c r="V28" s="108" t="n"/>
-      <c r="W28" s="280" t="inlineStr">
+      <c r="W28" s="279" t="inlineStr">
         <is>
           <t>PRE-CLOSE</t>
         </is>
@@ -14115,7 +13967,7 @@
           <t>4:45-930</t>
         </is>
       </c>
-      <c r="J29" s="215" t="n"/>
+      <c r="J29" s="211" t="n"/>
       <c r="K29" s="45" t="n"/>
       <c r="L29" s="45" t="n"/>
       <c r="M29" s="45" t="n"/>
@@ -14155,7 +14007,7 @@
           <t>4:45-930</t>
         </is>
       </c>
-      <c r="J30" s="215" t="n"/>
+      <c r="J30" s="211" t="n"/>
       <c r="K30" s="45" t="n"/>
       <c r="L30" s="45" t="n"/>
       <c r="M30" s="45" t="n"/>
@@ -14179,7 +14031,7 @@
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="263" t="inlineStr">
+      <c r="A31" s="252" t="inlineStr">
         <is>
           <t>BRAND ENVIRONMENT</t>
         </is>
@@ -14212,10 +14064,10 @@
           <t>SHIPMENT</t>
         </is>
       </c>
-      <c r="S31" s="241" t="n"/>
-      <c r="T31" s="241" t="n"/>
-      <c r="U31" s="241" t="n"/>
-      <c r="V31" s="241" t="n"/>
+      <c r="S31" s="231" t="n"/>
+      <c r="T31" s="231" t="n"/>
+      <c r="U31" s="231" t="n"/>
+      <c r="V31" s="231" t="n"/>
       <c r="W31" s="89" t="n"/>
       <c r="X31" s="127">
         <f>COUNTIF(#REF!,$R$46)+COUNTIF(#REF!,$S$46)+COUNTIF(#REF!,$M$46)+COUNTIF(#REF!,$N$46)+COUNTIF(#REF!,$O$46)+COUNTIF(#REF!,$P$46)+COUNTIF(#REF!,$Q$46)</f>
@@ -14239,7 +14091,7 @@
           <t>430-9</t>
         </is>
       </c>
-      <c r="J32" s="215" t="n"/>
+      <c r="J32" s="211" t="n"/>
       <c r="K32" s="45" t="n"/>
       <c r="L32" s="45" t="n"/>
       <c r="M32" s="45" t="n"/>
@@ -14252,10 +14104,10 @@
           <t>SHIPMENT</t>
         </is>
       </c>
-      <c r="S32" s="241" t="n"/>
-      <c r="T32" s="241" t="n"/>
-      <c r="U32" s="241" t="n"/>
-      <c r="V32" s="241" t="n"/>
+      <c r="S32" s="231" t="n"/>
+      <c r="T32" s="231" t="n"/>
+      <c r="U32" s="231" t="n"/>
+      <c r="V32" s="231" t="n"/>
       <c r="W32" s="89" t="n"/>
       <c r="X32" s="127">
         <f>COUNTIF(K31:V31,$R$46)+COUNTIF(K31:V31,$S$46)+COUNTIF(K31:V31,$M$46)+COUNTIF(K31:V31,$N$46)+COUNTIF(K31:V31,$O$46)+COUNTIF(K31:V31,$P$46)+COUNTIF(K31:V31,$Q$46)</f>
@@ -14291,7 +14143,7 @@
       </c>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="263" t="inlineStr">
+      <c r="A34" s="252" t="inlineStr">
         <is>
           <t>HEALTHY &amp; SAFETY</t>
         </is>
@@ -14379,7 +14231,7 @@
       </c>
     </row>
     <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="263" t="inlineStr">
+      <c r="A37" s="252" t="inlineStr">
         <is>
           <t>LOSS PREVENTION</t>
         </is>
@@ -14467,7 +14319,7 @@
       </c>
     </row>
     <row r="40" ht="27.75" customHeight="1">
-      <c r="A40" s="263" t="inlineStr">
+      <c r="A40" s="252" t="inlineStr">
         <is>
           <t>MARKETING</t>
         </is>
@@ -14546,7 +14398,7 @@
       <c r="X42" s="134" t="n"/>
     </row>
     <row r="43" ht="27.75" customHeight="1">
-      <c r="A43" s="263" t="inlineStr">
+      <c r="A43" s="252" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
@@ -14600,7 +14452,7 @@
       <c r="X44" s="134" t="n"/>
     </row>
     <row r="45" ht="27.75" customHeight="1">
-      <c r="A45" s="264" t="n"/>
+      <c r="A45" s="253" t="n"/>
       <c r="B45" s="375" t="n"/>
       <c r="C45" s="124" t="n"/>
       <c r="D45" s="96" t="n"/>
@@ -14640,7 +14492,7 @@
         </is>
       </c>
       <c r="J46" s="137" t="n"/>
-      <c r="K46" s="275" t="inlineStr">
+      <c r="K46" s="273" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
@@ -14755,7 +14607,7 @@
       <c r="W48" s="2" t="n"/>
       <c r="X48" s="134" t="n"/>
     </row>
-    <row r="49" hidden="1" ht="17.25" customHeight="1">
+    <row r="49" hidden="1" ht="18.75" customHeight="1">
       <c r="A49" s="159" t="n"/>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="124" t="n"/>
@@ -14879,7 +14731,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="88.5" customHeight="1">
@@ -14949,7 +14801,7 @@
         </is>
       </c>
       <c r="I3" s="362" t="n"/>
-      <c r="J3" s="249" t="n"/>
+      <c r="J3" s="238" t="n"/>
       <c r="K3" s="26" t="inlineStr">
         <is>
           <t>9am - 10am</t>
@@ -15036,7 +14888,7 @@
         </is>
       </c>
       <c r="I4" s="368" t="n"/>
-      <c r="J4" s="250" t="n"/>
+      <c r="J4" s="239" t="n"/>
       <c r="K4" s="36" t="n"/>
       <c r="L4" s="36" t="n">
         <v>0.01</v>
@@ -15099,7 +14951,7 @@
         </is>
       </c>
       <c r="I5" s="368" t="n"/>
-      <c r="J5" s="251" t="n"/>
+      <c r="J5" s="240" t="n"/>
       <c r="K5" s="38">
         <f>K4*B4</f>
         <v/>
@@ -15178,7 +15030,7 @@
         </is>
       </c>
       <c r="I6" s="368" t="n"/>
-      <c r="J6" s="251" t="n"/>
+      <c r="J6" s="240" t="n"/>
       <c r="K6" s="38">
         <f>K4*B5</f>
         <v/>
@@ -15249,7 +15101,7 @@
         </is>
       </c>
       <c r="I7" s="368" t="n"/>
-      <c r="J7" s="252" t="n"/>
+      <c r="J7" s="241" t="n"/>
       <c r="K7" s="45" t="n"/>
       <c r="L7" s="45" t="n"/>
       <c r="M7" s="45" t="n"/>
@@ -15296,7 +15148,7 @@
         </is>
       </c>
       <c r="I8" s="368" t="n"/>
-      <c r="J8" s="252" t="n"/>
+      <c r="J8" s="241" t="n"/>
       <c r="K8" s="47" t="n"/>
       <c r="L8" s="47" t="n"/>
       <c r="M8" s="47" t="n"/>
@@ -15328,7 +15180,7 @@
         </is>
       </c>
       <c r="I9" s="368" t="n"/>
-      <c r="J9" s="253" t="n"/>
+      <c r="J9" s="242" t="n"/>
       <c r="K9" s="47" t="n"/>
       <c r="L9" s="47" t="n"/>
       <c r="M9" s="47" t="n"/>
@@ -15358,7 +15210,7 @@
         </is>
       </c>
       <c r="I10" s="368" t="n"/>
-      <c r="J10" s="252" t="n"/>
+      <c r="J10" s="241" t="n"/>
       <c r="K10" s="49" t="n"/>
       <c r="L10" s="49" t="n"/>
       <c r="M10" s="49" t="n"/>
@@ -15390,7 +15242,7 @@
         </is>
       </c>
       <c r="I11" s="368" t="n"/>
-      <c r="J11" s="252" t="n"/>
+      <c r="J11" s="241" t="n"/>
       <c r="K11" s="50" t="n"/>
       <c r="L11" s="50" t="n"/>
       <c r="M11" s="50" t="n"/>
@@ -15422,7 +15274,7 @@
         </is>
       </c>
       <c r="I12" s="368" t="n"/>
-      <c r="J12" s="252" t="n"/>
+      <c r="J12" s="241" t="n"/>
       <c r="K12" s="45" t="n"/>
       <c r="L12" s="45" t="n"/>
       <c r="M12" s="45" t="n"/>
@@ -15454,7 +15306,7 @@
         </is>
       </c>
       <c r="I13" s="368" t="n"/>
-      <c r="J13" s="254" t="n"/>
+      <c r="J13" s="243" t="n"/>
       <c r="K13" s="45" t="n"/>
       <c r="L13" s="45" t="n"/>
       <c r="M13" s="45" t="n"/>
@@ -15484,7 +15336,7 @@
         </is>
       </c>
       <c r="I14" s="372" t="n"/>
-      <c r="J14" s="255" t="n"/>
+      <c r="J14" s="244" t="n"/>
       <c r="K14" s="61" t="n"/>
       <c r="L14" s="61" t="n"/>
       <c r="M14" s="61" t="n"/>
@@ -15534,7 +15386,7 @@
           <t>MONTH TO DATE SALES</t>
         </is>
       </c>
-      <c r="B16" s="266" t="n"/>
+      <c r="B16" s="255" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="H16" s="69" t="inlineStr">
         <is>
@@ -15644,54 +15496,54 @@
       </c>
       <c r="B18" s="80" t="n"/>
       <c r="C18" s="3" t="n"/>
-      <c r="H18" s="98" t="inlineStr">
-        <is>
-          <t>DARCY</t>
-        </is>
-      </c>
-      <c r="I18" s="99" t="inlineStr">
-        <is>
-          <t>8-430</t>
-        </is>
-      </c>
-      <c r="J18" s="210" t="inlineStr">
-        <is>
-          <t>OFFICE</t>
-        </is>
-      </c>
-      <c r="K18" s="55" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="L18" s="49" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="M18" s="86" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="N18" s="49" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="O18" s="86" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="P18" s="49" t="inlineStr">
-        <is>
-          <t>MENS</t>
-        </is>
-      </c>
-      <c r="Q18" s="179" t="inlineStr">
-        <is>
-          <t>MENS</t>
+      <c r="H18" s="256" t="inlineStr">
+        <is>
+          <t>Kaur, Taranpreet</t>
+        </is>
+      </c>
+      <c r="I18" s="257" t="inlineStr">
+        <is>
+          <t>08:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="J18" s="258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" s="259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" s="261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" s="261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q18" s="262" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="R18" s="45" t="n"/>
@@ -15702,9 +15554,9 @@
       <c r="W18" s="189" t="n"/>
       <c r="X18" s="56" t="n"/>
     </row>
-    <row r="19" hidden="1" ht="17.25" customHeight="1">
+    <row r="19" hidden="1" ht="18.75" customHeight="1">
       <c r="A19" s="94" t="n"/>
-      <c r="B19" s="257">
+      <c r="B19" s="246">
         <f>B15+B18</f>
         <v/>
       </c>
@@ -15715,19 +15567,39 @@
       <c r="G19" s="97" t="n"/>
       <c r="H19" s="98" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>Herbert, Rebecca</t>
         </is>
       </c>
       <c r="I19" s="99" t="inlineStr">
         <is>
-          <t>2-7</t>
-        </is>
-      </c>
-      <c r="J19" s="215" t="n"/>
-      <c r="K19" s="45" t="n"/>
-      <c r="L19" s="45" t="n"/>
-      <c r="M19" s="45" t="n"/>
-      <c r="N19" s="45" t="n"/>
+          <t>08:00 - 12:45</t>
+        </is>
+      </c>
+      <c r="J19" s="211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O19" s="45" t="n"/>
       <c r="P19" s="45" t="n"/>
       <c r="Q19" s="45" t="n"/>
@@ -15739,7 +15611,7 @@
       <c r="W19" s="189" t="n"/>
       <c r="X19" s="56" t="n"/>
     </row>
-    <row r="20" hidden="1" ht="17.25" customHeight="1">
+    <row r="20" hidden="1" ht="18.75" customHeight="1">
       <c r="A20" s="100" t="n"/>
       <c r="B20" s="101" t="n">
         <v>1</v>
@@ -15751,23 +15623,55 @@
       <c r="G20" s="97" t="n"/>
       <c r="H20" s="98" t="inlineStr">
         <is>
-          <t>TARAN</t>
+          <t>Hipkiss, Darcy</t>
         </is>
       </c>
       <c r="I20" s="99" t="inlineStr">
         <is>
-          <t>1-930</t>
-        </is>
-      </c>
-      <c r="J20" s="215" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
-      <c r="M20" s="45" t="n"/>
-      <c r="N20" s="45" t="n"/>
-      <c r="O20" s="45" t="n"/>
-      <c r="P20" s="45" t="n"/>
-      <c r="Q20" s="45" t="n"/>
-      <c r="R20" s="45" t="n"/>
+          <t>09:00 - 05:30</t>
+        </is>
+      </c>
+      <c r="J20" s="211" t="n"/>
+      <c r="K20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S20" s="45" t="n"/>
       <c r="T20" s="45" t="n"/>
       <c r="U20" s="45" t="n"/>
@@ -15783,34 +15687,58 @@
       <c r="E21" s="96" t="n"/>
       <c r="F21" s="96" t="n"/>
       <c r="G21" s="97" t="n"/>
-      <c r="H21" s="98" t="inlineStr">
-        <is>
-          <t>SAIGE</t>
-        </is>
-      </c>
-      <c r="I21" s="99" t="inlineStr">
-        <is>
-          <t>8-12:45</t>
-        </is>
-      </c>
-      <c r="J21" s="210" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="K21" s="55" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="L21" s="110" t="n"/>
-      <c r="M21" s="110" t="n"/>
-      <c r="N21" s="110" t="n"/>
-      <c r="O21" s="45" t="n"/>
-      <c r="P21" s="45" t="n"/>
-      <c r="Q21" s="45" t="n"/>
-      <c r="R21" s="45" t="n"/>
-      <c r="S21" s="45" t="n"/>
+      <c r="H21" s="256" t="inlineStr">
+        <is>
+          <t>Parmar, Amita</t>
+        </is>
+      </c>
+      <c r="I21" s="257" t="inlineStr">
+        <is>
+          <t>10:00 - 06:30</t>
+        </is>
+      </c>
+      <c r="J21" s="258" t="inlineStr"/>
+      <c r="K21" s="259" t="inlineStr"/>
+      <c r="L21" s="110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" s="110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" s="110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q21" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S21" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T21" s="45" t="n"/>
       <c r="U21" s="45" t="n"/>
       <c r="V21" s="45" t="n"/>
@@ -15828,38 +15756,46 @@
       <c r="E22" s="96" t="n"/>
       <c r="F22" s="96" t="n"/>
       <c r="G22" s="97" t="n"/>
-      <c r="H22" s="98" t="inlineStr">
-        <is>
-          <t>SIERRA</t>
-        </is>
-      </c>
-      <c r="I22" s="99" t="inlineStr">
-        <is>
-          <t>10-630</t>
-        </is>
-      </c>
-      <c r="J22" s="210" t="n"/>
+      <c r="H22" s="256" t="inlineStr">
+        <is>
+          <t>Bruce, Saige</t>
+        </is>
+      </c>
+      <c r="I22" s="257" t="inlineStr">
+        <is>
+          <t>10:15 - 03:00</t>
+        </is>
+      </c>
+      <c r="J22" s="209" t="n"/>
       <c r="K22" s="45" t="n"/>
-      <c r="L22" s="49" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="M22" s="267" t="n"/>
-      <c r="N22" s="49" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="O22" s="268" t="n"/>
-      <c r="P22" s="268" t="n"/>
-      <c r="Q22" s="268" t="n"/>
-      <c r="R22" s="49" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="S22" s="267" t="n"/>
+      <c r="L22" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" s="263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" s="264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" s="264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q22" s="264" t="n"/>
+      <c r="R22" s="260" t="inlineStr"/>
+      <c r="S22" s="263" t="n"/>
       <c r="T22" s="45" t="n"/>
       <c r="U22" s="45" t="n"/>
       <c r="V22" s="45" t="n"/>
@@ -15877,28 +15813,44 @@
       <c r="E23" s="96" t="n"/>
       <c r="F23" s="96" t="n"/>
       <c r="G23" s="97" t="n"/>
-      <c r="H23" s="98" t="inlineStr">
-        <is>
-          <t>NAAIJA</t>
-        </is>
-      </c>
-      <c r="I23" s="99" t="inlineStr">
-        <is>
-          <t>1115-4</t>
-        </is>
-      </c>
-      <c r="J23" s="210" t="n"/>
+      <c r="H23" s="256" t="inlineStr">
+        <is>
+          <t>Alabi, Ibukun</t>
+        </is>
+      </c>
+      <c r="I23" s="257" t="inlineStr">
+        <is>
+          <t>11:15 - 04:00</t>
+        </is>
+      </c>
+      <c r="J23" s="209" t="n"/>
       <c r="K23" s="45" t="n"/>
       <c r="L23" s="45" t="n"/>
-      <c r="M23" s="258" t="inlineStr">
-        <is>
-          <t>MENS</t>
-        </is>
-      </c>
-      <c r="N23" s="104" t="n"/>
-      <c r="O23" s="104" t="n"/>
-      <c r="P23" s="104" t="n"/>
-      <c r="Q23" s="104" t="n"/>
+      <c r="M23" s="265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q23" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R23" s="45" t="n"/>
       <c r="S23" s="45" t="n"/>
       <c r="T23" s="45" t="n"/>
@@ -15918,28 +15870,44 @@
       <c r="E24" s="96" t="n"/>
       <c r="F24" s="96" t="n"/>
       <c r="G24" s="97" t="n"/>
-      <c r="H24" s="98" t="inlineStr">
-        <is>
-          <t>AMITA</t>
-        </is>
-      </c>
-      <c r="I24" s="99" t="inlineStr">
-        <is>
-          <t>1215-5</t>
-        </is>
-      </c>
-      <c r="J24" s="210" t="n"/>
+      <c r="H24" s="256" t="inlineStr">
+        <is>
+          <t>Haydu, Maria</t>
+        </is>
+      </c>
+      <c r="I24" s="257" t="inlineStr">
+        <is>
+          <t>11:15 - 04:00</t>
+        </is>
+      </c>
+      <c r="J24" s="209" t="n"/>
       <c r="K24" s="45" t="n"/>
       <c r="L24" s="45" t="n"/>
-      <c r="M24" s="45" t="n"/>
-      <c r="N24" s="269" t="inlineStr">
-        <is>
-          <t>FITS</t>
-        </is>
-      </c>
-      <c r="O24" s="108" t="n"/>
-      <c r="P24" s="108" t="n"/>
-      <c r="Q24" s="108" t="n"/>
+      <c r="M24" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N24" s="266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q24" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R24" s="108" t="n"/>
       <c r="S24" s="45" t="n"/>
       <c r="T24" s="45" t="n"/>
@@ -15956,29 +15924,45 @@
       <c r="E25" s="96" t="n"/>
       <c r="F25" s="96" t="n"/>
       <c r="G25" s="97" t="n"/>
-      <c r="H25" s="98" t="inlineStr">
-        <is>
-          <t>AVERY</t>
-        </is>
-      </c>
-      <c r="I25" s="99" t="inlineStr">
-        <is>
-          <t>1215-5</t>
-        </is>
-      </c>
-      <c r="J25" s="210" t="n"/>
+      <c r="H25" s="256" t="inlineStr">
+        <is>
+          <t>Kaur, Rupinder</t>
+        </is>
+      </c>
+      <c r="I25" s="257" t="inlineStr">
+        <is>
+          <t>12:15 - 05:00</t>
+        </is>
+      </c>
+      <c r="J25" s="209" t="n"/>
       <c r="K25" s="45" t="n"/>
       <c r="L25" s="45" t="n"/>
       <c r="M25" s="45" t="n"/>
-      <c r="N25" s="269" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="O25" s="93" t="n"/>
-      <c r="P25" s="93" t="n"/>
-      <c r="Q25" s="93" t="n"/>
-      <c r="R25" s="93" t="n"/>
+      <c r="N25" s="266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q25" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S25" s="45" t="n"/>
       <c r="T25" s="45" t="n"/>
       <c r="U25" s="45" t="n"/>
@@ -15987,195 +15971,251 @@
       <c r="X25" s="56" t="n"/>
     </row>
     <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="270" t="n"/>
+      <c r="A26" s="267" t="n"/>
       <c r="B26" s="118" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="96" t="n"/>
       <c r="E26" s="96" t="n"/>
       <c r="F26" s="96" t="n"/>
       <c r="G26" s="97" t="n"/>
-      <c r="H26" s="98" t="inlineStr">
-        <is>
-          <t>HARNOOR</t>
-        </is>
-      </c>
-      <c r="I26" s="99" t="inlineStr">
-        <is>
-          <t>1215-5</t>
-        </is>
-      </c>
-      <c r="J26" s="210" t="n"/>
+      <c r="H26" s="256" t="inlineStr">
+        <is>
+          <t>Thompson, Sierra</t>
+        </is>
+      </c>
+      <c r="I26" s="257" t="inlineStr">
+        <is>
+          <t>01:00 - 09:30</t>
+        </is>
+      </c>
+      <c r="J26" s="209" t="n"/>
       <c r="K26" s="45" t="n"/>
       <c r="L26" s="45" t="n"/>
       <c r="M26" s="45" t="n"/>
-      <c r="N26" s="269" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="O26" s="93" t="n"/>
-      <c r="P26" s="93" t="n"/>
-      <c r="Q26" s="93" t="n"/>
-      <c r="R26" s="93" t="n"/>
-      <c r="S26" s="45" t="n"/>
-      <c r="T26" s="45" t="n"/>
-      <c r="U26" s="45" t="n"/>
-      <c r="V26" s="45" t="n"/>
+      <c r="N26" s="266" t="inlineStr"/>
+      <c r="O26" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q26" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S26" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T26" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U26" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W26" s="89" t="n"/>
       <c r="X26" s="56" t="n"/>
     </row>
     <row r="27" ht="27.75" customHeight="1">
-      <c r="A27" s="270" t="n"/>
+      <c r="A27" s="267" t="n"/>
       <c r="B27" s="118" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="96" t="n"/>
       <c r="E27" s="96" t="n"/>
       <c r="F27" s="96" t="n"/>
       <c r="G27" s="97" t="n"/>
-      <c r="H27" s="98" t="inlineStr">
-        <is>
-          <t>KIRAN</t>
-        </is>
-      </c>
-      <c r="I27" s="99" t="inlineStr">
-        <is>
-          <t>1215-5</t>
-        </is>
-      </c>
-      <c r="J27" s="210" t="n"/>
+      <c r="H27" s="256" t="inlineStr">
+        <is>
+          <t>Piguing, Trisha Mae</t>
+        </is>
+      </c>
+      <c r="I27" s="257" t="inlineStr">
+        <is>
+          <t>02:15 - 07:00</t>
+        </is>
+      </c>
+      <c r="J27" s="209" t="n"/>
       <c r="K27" s="45" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="45" t="n"/>
-      <c r="N27" s="269" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="O27" s="268" t="n"/>
-      <c r="P27" s="268" t="n"/>
-      <c r="Q27" s="268" t="n"/>
-      <c r="R27" s="268" t="n"/>
-      <c r="S27" s="45" t="n"/>
-      <c r="T27" s="45" t="n"/>
+      <c r="N27" s="266" t="inlineStr"/>
+      <c r="O27" s="264" t="n"/>
+      <c r="P27" s="264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q27" s="264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" s="264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S27" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T27" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U27" s="45" t="n"/>
       <c r="V27" s="45" t="n"/>
       <c r="W27" s="89" t="n"/>
       <c r="X27" s="56" t="n"/>
     </row>
     <row r="28" ht="27.75" customHeight="1">
-      <c r="A28" s="271" t="n"/>
+      <c r="A28" s="268" t="n"/>
       <c r="B28" s="121" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="96" t="n"/>
       <c r="E28" s="96" t="n"/>
       <c r="F28" s="96" t="n"/>
       <c r="G28" s="97" t="n"/>
-      <c r="H28" s="98" t="inlineStr">
-        <is>
-          <t>RICKY</t>
-        </is>
-      </c>
-      <c r="I28" s="99" t="inlineStr">
-        <is>
-          <t>1-930</t>
-        </is>
-      </c>
-      <c r="J28" s="215" t="n"/>
+      <c r="H28" s="256" t="inlineStr">
+        <is>
+          <t>Camaso-Catalan, Lesley</t>
+        </is>
+      </c>
+      <c r="I28" s="257" t="inlineStr">
+        <is>
+          <t>04:30 - 09:00</t>
+        </is>
+      </c>
+      <c r="J28" s="211" t="n"/>
       <c r="K28" s="45" t="n"/>
       <c r="L28" s="45" t="n"/>
       <c r="M28" s="45" t="n"/>
       <c r="N28" s="45" t="n"/>
-      <c r="O28" s="49" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="P28" s="49" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="Q28" s="267" t="n"/>
-      <c r="R28" s="49" t="inlineStr">
-        <is>
-          <t>FLEX</t>
-        </is>
-      </c>
-      <c r="S28" s="125" t="n"/>
-      <c r="T28" s="49" t="inlineStr">
-        <is>
-          <t>CEL</t>
-        </is>
-      </c>
-      <c r="U28" s="267" t="n"/>
-      <c r="V28" s="267" t="n"/>
+      <c r="O28" s="260" t="inlineStr"/>
+      <c r="P28" s="260" t="inlineStr"/>
+      <c r="Q28" s="263" t="n"/>
+      <c r="R28" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S28" s="125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T28" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U28" s="263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" s="263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" s="189" t="n"/>
       <c r="X28" s="127" t="n"/>
     </row>
     <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="271" t="n"/>
+      <c r="A29" s="268" t="n"/>
       <c r="B29" s="121" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="96" t="n"/>
       <c r="E29" s="96" t="n"/>
       <c r="F29" s="96" t="n"/>
       <c r="G29" s="97" t="n"/>
-      <c r="H29" s="98" t="inlineStr">
-        <is>
-          <t>LELAND</t>
-        </is>
-      </c>
-      <c r="I29" s="99" t="inlineStr">
-        <is>
-          <t>215-7</t>
-        </is>
-      </c>
-      <c r="J29" s="215" t="n"/>
+      <c r="H29" s="256" t="inlineStr">
+        <is>
+          <t>Frandsen, Ella</t>
+        </is>
+      </c>
+      <c r="I29" s="257" t="inlineStr">
+        <is>
+          <t>04:30 - 09:00</t>
+        </is>
+      </c>
+      <c r="J29" s="211" t="n"/>
       <c r="K29" s="45" t="n"/>
       <c r="L29" s="45" t="n"/>
       <c r="M29" s="45" t="n"/>
       <c r="N29" s="45" t="n"/>
       <c r="O29" s="45" t="n"/>
-      <c r="P29" s="49" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="Q29" s="92" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="R29" s="49" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="S29" s="105" t="n"/>
-      <c r="T29" s="105" t="n"/>
-      <c r="U29" s="45" t="n"/>
-      <c r="V29" s="45" t="n"/>
+      <c r="P29" s="260" t="inlineStr"/>
+      <c r="Q29" s="269" t="inlineStr"/>
+      <c r="R29" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S29" s="105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T29" s="105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U29" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" s="45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" s="189" t="n"/>
       <c r="X29" s="127" t="n"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="272" t="n"/>
+      <c r="A30" s="270" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="96" t="n"/>
       <c r="E30" s="96" t="n"/>
       <c r="F30" s="96" t="n"/>
       <c r="G30" s="97" t="n"/>
-      <c r="H30" s="98" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="I30" s="99" t="inlineStr">
-        <is>
-          <t>445-930</t>
-        </is>
-      </c>
-      <c r="J30" s="215" t="n"/>
+      <c r="H30" s="256" t="inlineStr">
+        <is>
+          <t>Mendoza, Ava</t>
+        </is>
+      </c>
+      <c r="I30" s="257" t="inlineStr">
+        <is>
+          <t>04:45 - 09:30</t>
+        </is>
+      </c>
+      <c r="J30" s="211" t="n"/>
       <c r="K30" s="45" t="n"/>
       <c r="L30" s="45" t="n"/>
       <c r="M30" s="45" t="n"/>
@@ -16183,37 +16223,53 @@
       <c r="O30" s="45" t="n"/>
       <c r="P30" s="45" t="n"/>
       <c r="Q30" s="45" t="n"/>
-      <c r="R30" s="49" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="S30" s="93" t="n"/>
-      <c r="T30" s="93" t="n"/>
-      <c r="U30" s="93" t="n"/>
-      <c r="V30" s="93" t="n"/>
+      <c r="R30" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S30" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T30" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U30" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" s="93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" s="89" t="n"/>
       <c r="X30" s="127" t="n"/>
     </row>
     <row r="31" ht="27.75" customHeight="1">
       <c r="A31" s="186" t="n"/>
-      <c r="B31" s="273" t="n"/>
+      <c r="B31" s="271" t="n"/>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="96" t="n"/>
       <c r="E31" s="96" t="n"/>
       <c r="F31" s="96" t="n"/>
       <c r="G31" s="97" t="n"/>
-      <c r="H31" s="98" t="inlineStr">
-        <is>
-          <t>AVA M</t>
-        </is>
-      </c>
-      <c r="I31" s="99" t="inlineStr">
-        <is>
-          <t>445-930</t>
-        </is>
-      </c>
-      <c r="J31" s="215" t="n"/>
+      <c r="H31" s="256" t="inlineStr">
+        <is>
+          <t>Sidhu, Jasmin</t>
+        </is>
+      </c>
+      <c r="I31" s="257" t="inlineStr">
+        <is>
+          <t>04:45 - 09:30</t>
+        </is>
+      </c>
+      <c r="J31" s="211" t="n"/>
       <c r="K31" s="45" t="n"/>
       <c r="L31" s="45" t="n"/>
       <c r="M31" s="45" t="n"/>
@@ -16221,37 +16277,53 @@
       <c r="O31" s="45" t="n"/>
       <c r="P31" s="45" t="n"/>
       <c r="Q31" s="45" t="n"/>
-      <c r="R31" s="49" t="inlineStr">
-        <is>
-          <t>MENS</t>
-        </is>
-      </c>
-      <c r="S31" s="104" t="n"/>
-      <c r="T31" s="104" t="n"/>
-      <c r="U31" s="104" t="n"/>
-      <c r="V31" s="104" t="n"/>
+      <c r="R31" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S31" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T31" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U31" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" s="104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" s="89" t="n"/>
       <c r="X31" s="127" t="n"/>
     </row>
     <row r="32" ht="27.75" customHeight="1">
       <c r="A32" s="186" t="n"/>
-      <c r="B32" s="273" t="n"/>
+      <c r="B32" s="271" t="n"/>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="96" t="n"/>
       <c r="E32" s="96" t="n"/>
       <c r="F32" s="96" t="n"/>
       <c r="G32" s="97" t="n"/>
-      <c r="H32" s="98" t="inlineStr">
-        <is>
-          <t>SHAE</t>
-        </is>
-      </c>
-      <c r="I32" s="99" t="inlineStr">
-        <is>
-          <t>445-930</t>
-        </is>
-      </c>
-      <c r="J32" s="215" t="n"/>
+      <c r="H32" s="256" t="inlineStr">
+        <is>
+          <t>Tapping, Sarah</t>
+        </is>
+      </c>
+      <c r="I32" s="257" t="inlineStr">
+        <is>
+          <t>04:45 - 09:30</t>
+        </is>
+      </c>
+      <c r="J32" s="211" t="n"/>
       <c r="K32" s="45" t="n"/>
       <c r="L32" s="45" t="n"/>
       <c r="M32" s="45" t="n"/>
@@ -16259,37 +16331,45 @@
       <c r="O32" s="45" t="n"/>
       <c r="P32" s="45" t="n"/>
       <c r="Q32" s="45" t="n"/>
-      <c r="R32" s="49" t="inlineStr">
-        <is>
-          <t>FITS</t>
-        </is>
-      </c>
-      <c r="S32" s="108" t="n"/>
-      <c r="T32" s="108" t="n"/>
-      <c r="U32" s="108" t="n"/>
-      <c r="V32" s="108" t="n"/>
+      <c r="R32" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S32" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T32" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U32" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" s="108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" s="89" t="n"/>
       <c r="X32" s="127" t="n"/>
     </row>
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="186" t="n"/>
-      <c r="B33" s="273" t="n"/>
+      <c r="B33" s="271" t="n"/>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="96" t="n"/>
       <c r="E33" s="96" t="n"/>
       <c r="F33" s="96" t="n"/>
       <c r="G33" s="97" t="n"/>
-      <c r="H33" s="98" t="inlineStr">
-        <is>
-          <t>LESLEY</t>
-        </is>
-      </c>
-      <c r="I33" s="99" t="inlineStr">
-        <is>
-          <t>430-9</t>
-        </is>
-      </c>
-      <c r="J33" s="215" t="n"/>
+      <c r="H33" s="256" t="inlineStr"/>
+      <c r="I33" s="257" t="inlineStr"/>
+      <c r="J33" s="211" t="n"/>
       <c r="K33" s="45" t="n"/>
       <c r="L33" s="45" t="n"/>
       <c r="M33" s="45" t="n"/>
@@ -16297,15 +16377,11 @@
       <c r="O33" s="45" t="n"/>
       <c r="P33" s="45" t="n"/>
       <c r="Q33" s="45" t="n"/>
-      <c r="R33" s="49" t="inlineStr">
-        <is>
-          <t>SHIPMENT</t>
-        </is>
-      </c>
-      <c r="S33" s="241" t="n"/>
-      <c r="T33" s="241" t="n"/>
-      <c r="U33" s="241" t="n"/>
-      <c r="V33" s="241" t="n"/>
+      <c r="R33" s="260" t="inlineStr"/>
+      <c r="S33" s="231" t="n"/>
+      <c r="T33" s="231" t="n"/>
+      <c r="U33" s="231" t="n"/>
+      <c r="V33" s="231" t="n"/>
       <c r="W33" s="89" t="n"/>
       <c r="X33" s="127" t="n"/>
     </row>
@@ -16316,17 +16392,9 @@
       <c r="E34" s="96" t="n"/>
       <c r="F34" s="96" t="n"/>
       <c r="G34" s="97" t="n"/>
-      <c r="H34" s="98" t="inlineStr">
-        <is>
-          <t>PEYTON</t>
-        </is>
-      </c>
-      <c r="I34" s="99" t="inlineStr">
-        <is>
-          <t>430-9</t>
-        </is>
-      </c>
-      <c r="J34" s="215" t="n"/>
+      <c r="H34" s="256" t="inlineStr"/>
+      <c r="I34" s="257" t="inlineStr"/>
+      <c r="J34" s="211" t="n"/>
       <c r="K34" s="45" t="n"/>
       <c r="L34" s="45" t="n"/>
       <c r="M34" s="45" t="n"/>
@@ -16334,17 +16402,13 @@
       <c r="O34" s="45" t="n"/>
       <c r="P34" s="45" t="n"/>
       <c r="Q34" s="45" t="n"/>
-      <c r="R34" s="49" t="inlineStr">
-        <is>
-          <t>SHIPMENT</t>
-        </is>
-      </c>
-      <c r="S34" s="241" t="n"/>
-      <c r="T34" s="241" t="n"/>
-      <c r="U34" s="241" t="n"/>
-      <c r="V34" s="241" t="n"/>
+      <c r="R34" s="260" t="inlineStr"/>
+      <c r="S34" s="231" t="n"/>
+      <c r="T34" s="231" t="n"/>
+      <c r="U34" s="231" t="n"/>
+      <c r="V34" s="231" t="n"/>
       <c r="W34" s="89" t="n"/>
-      <c r="X34" s="274" t="inlineStr">
+      <c r="X34" s="272" t="inlineStr">
         <is>
           <t>SELLING HOURS</t>
         </is>
@@ -16359,7 +16423,7 @@
       <c r="G35" s="97" t="n"/>
       <c r="H35" s="98" t="n"/>
       <c r="I35" s="129" t="n"/>
-      <c r="J35" s="215" t="n"/>
+      <c r="J35" s="211" t="n"/>
       <c r="K35" s="45" t="n"/>
       <c r="L35" s="45" t="n"/>
       <c r="M35" s="45" t="n"/>
@@ -16387,7 +16451,7 @@
       <c r="G36" s="97" t="n"/>
       <c r="H36" s="98" t="n"/>
       <c r="I36" s="129" t="n"/>
-      <c r="J36" s="215" t="n"/>
+      <c r="J36" s="211" t="n"/>
       <c r="K36" s="45" t="n"/>
       <c r="L36" s="45" t="n"/>
       <c r="M36" s="45" t="n"/>
@@ -16407,7 +16471,7 @@
       </c>
     </row>
     <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="263" t="inlineStr">
+      <c r="A37" s="252" t="inlineStr">
         <is>
           <t>CONSUMER EXPERIENCE</t>
         </is>
@@ -16419,7 +16483,7 @@
       <c r="G37" s="97" t="n"/>
       <c r="H37" s="98" t="n"/>
       <c r="I37" s="129" t="n"/>
-      <c r="J37" s="215" t="n"/>
+      <c r="J37" s="211" t="n"/>
       <c r="K37" s="45" t="n"/>
       <c r="L37" s="45" t="n"/>
       <c r="M37" s="45" t="n"/>
@@ -16451,7 +16515,7 @@
       <c r="G38" s="97" t="n"/>
       <c r="H38" s="98" t="n"/>
       <c r="I38" s="129" t="n"/>
-      <c r="J38" s="215" t="n"/>
+      <c r="J38" s="211" t="n"/>
       <c r="K38" s="45" t="n"/>
       <c r="L38" s="45" t="n"/>
       <c r="M38" s="45" t="n"/>
@@ -16531,7 +16595,7 @@
       </c>
     </row>
     <row r="41" ht="27.75" customHeight="1">
-      <c r="A41" s="263" t="inlineStr">
+      <c r="A41" s="252" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
@@ -16647,7 +16711,7 @@
       </c>
     </row>
     <row r="45" ht="27.75" customHeight="1">
-      <c r="A45" s="263" t="inlineStr">
+      <c r="A45" s="252" t="inlineStr">
         <is>
           <t>HR &amp; PEOPLE</t>
         </is>
@@ -16735,7 +16799,7 @@
       </c>
     </row>
     <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="263" t="inlineStr">
+      <c r="A48" s="252" t="inlineStr">
         <is>
           <t>BRAND ENVIRONMENT</t>
         </is>
@@ -16808,7 +16872,7 @@
         </is>
       </c>
       <c r="J50" s="137" t="n"/>
-      <c r="K50" s="275" t="inlineStr">
+      <c r="K50" s="273" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
@@ -16875,7 +16939,7 @@
       </c>
     </row>
     <row r="51" ht="27.75" customHeight="1">
-      <c r="A51" s="263" t="inlineStr">
+      <c r="A51" s="252" t="inlineStr">
         <is>
           <t>HEALTHY &amp; SAFETY</t>
         </is>
@@ -16971,7 +17035,7 @@
       </c>
     </row>
     <row r="54" ht="27.75" customHeight="1">
-      <c r="A54" s="263" t="inlineStr">
+      <c r="A54" s="252" t="inlineStr">
         <is>
           <t>LOSS PREVENTION</t>
         </is>
@@ -17067,7 +17131,7 @@
       </c>
     </row>
     <row r="57" ht="27.75" customHeight="1">
-      <c r="A57" s="263" t="inlineStr">
+      <c r="A57" s="252" t="inlineStr">
         <is>
           <t>MARKETING</t>
         </is>
@@ -17154,7 +17218,7 @@
       <c r="X59" s="134" t="n"/>
     </row>
     <row r="60" ht="27.75" customHeight="1">
-      <c r="A60" s="263" t="inlineStr">
+      <c r="A60" s="252" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
@@ -17212,7 +17276,7 @@
       <c r="X61" s="134" t="n"/>
     </row>
     <row r="62" ht="27.75" customHeight="1">
-      <c r="A62" s="264" t="n"/>
+      <c r="A62" s="253" t="n"/>
       <c r="B62" s="375" t="n"/>
       <c r="C62" s="124" t="n"/>
       <c r="D62" s="96" t="n"/>
@@ -17315,7 +17379,7 @@
       <c r="W65" s="2" t="n"/>
       <c r="X65" s="134" t="n"/>
     </row>
-    <row r="66" hidden="1" ht="17.25" customHeight="1">
+    <row r="66" hidden="1" ht="18.75" customHeight="1">
       <c r="A66" s="159" t="n"/>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="124" t="n"/>
@@ -17437,7 +17501,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="165" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="88.5" customHeight="1">
@@ -17511,8 +17575,8 @@
         </is>
       </c>
       <c r="I3" s="362" t="n"/>
-      <c r="J3" s="249" t="n"/>
-      <c r="K3" s="249" t="n"/>
+      <c r="J3" s="238" t="n"/>
+      <c r="K3" s="238" t="n"/>
       <c r="L3" s="25" t="inlineStr">
         <is>
           <t>10am - 11am</t>
@@ -17594,8 +17658,8 @@
         </is>
       </c>
       <c r="I4" s="368" t="n"/>
-      <c r="J4" s="250" t="n"/>
-      <c r="K4" s="250" t="n"/>
+      <c r="J4" s="239" t="n"/>
+      <c r="K4" s="239" t="n"/>
       <c r="L4" s="36" t="n">
         <v>0.03</v>
       </c>
@@ -17657,8 +17721,8 @@
         </is>
       </c>
       <c r="I5" s="368" t="n"/>
-      <c r="J5" s="251" t="n"/>
-      <c r="K5" s="251" t="n"/>
+      <c r="J5" s="240" t="n"/>
+      <c r="K5" s="240" t="n"/>
       <c r="L5" s="38">
         <f>SUM(L$4:L$4)*$B$4</f>
         <v/>
@@ -17733,8 +17797,8 @@
         </is>
       </c>
       <c r="I6" s="368" t="n"/>
-      <c r="J6" s="251" t="n"/>
-      <c r="K6" s="251" t="n"/>
+      <c r="J6" s="240" t="n"/>
+      <c r="K6" s="240" t="n"/>
       <c r="L6" s="38">
         <f>SUM(L4:L4)*$B$5</f>
         <v/>
@@ -17801,8 +17865,8 @@
         </is>
       </c>
       <c r="I7" s="368" t="n"/>
-      <c r="J7" s="252" t="n"/>
-      <c r="K7" s="252" t="n"/>
+      <c r="J7" s="241" t="n"/>
+      <c r="K7" s="241" t="n"/>
       <c r="L7" s="45" t="n"/>
       <c r="M7" s="45" t="n"/>
       <c r="N7" s="45" t="n"/>
@@ -17848,8 +17912,8 @@
         </is>
       </c>
       <c r="I8" s="368" t="n"/>
-      <c r="J8" s="252" t="n"/>
-      <c r="K8" s="252" t="n"/>
+      <c r="J8" s="241" t="n"/>
+      <c r="K8" s="241" t="n"/>
       <c r="L8" s="47" t="n"/>
       <c r="M8" s="47" t="n"/>
       <c r="N8" s="47" t="n"/>
@@ -17880,8 +17944,8 @@
         </is>
       </c>
       <c r="I9" s="368" t="n"/>
-      <c r="J9" s="253" t="n"/>
-      <c r="K9" s="253" t="n"/>
+      <c r="J9" s="242" t="n"/>
+      <c r="K9" s="242" t="n"/>
       <c r="L9" s="47" t="n"/>
       <c r="M9" s="47" t="n"/>
       <c r="N9" s="47" t="n"/>
@@ -17912,8 +17976,8 @@
         </is>
       </c>
       <c r="I10" s="368" t="n"/>
-      <c r="J10" s="252" t="n"/>
-      <c r="K10" s="252" t="n"/>
+      <c r="J10" s="241" t="n"/>
+      <c r="K10" s="241" t="n"/>
       <c r="L10" s="49" t="n"/>
       <c r="M10" s="49" t="n"/>
       <c r="N10" s="49" t="n"/>
@@ -17944,8 +18008,8 @@
         </is>
       </c>
       <c r="I11" s="368" t="n"/>
-      <c r="J11" s="252" t="n"/>
-      <c r="K11" s="252" t="n"/>
+      <c r="J11" s="241" t="n"/>
+      <c r="K11" s="241" t="n"/>
       <c r="L11" s="50" t="n"/>
       <c r="M11" s="50" t="n"/>
       <c r="N11" s="50" t="n"/>
@@ -17976,8 +18040,8 @@
         </is>
       </c>
       <c r="I12" s="368" t="n"/>
-      <c r="J12" s="252" t="n"/>
-      <c r="K12" s="252" t="n"/>
+      <c r="J12" s="241" t="n"/>
+      <c r="K12" s="241" t="n"/>
       <c r="L12" s="45" t="n"/>
       <c r="M12" s="45" t="n"/>
       <c r="N12" s="45" t="n"/>
@@ -18008,8 +18072,8 @@
         </is>
       </c>
       <c r="I13" s="368" t="n"/>
-      <c r="J13" s="254" t="n"/>
-      <c r="K13" s="254" t="n"/>
+      <c r="J13" s="243" t="n"/>
+      <c r="K13" s="243" t="n"/>
       <c r="L13" s="45" t="n"/>
       <c r="M13" s="45" t="n"/>
       <c r="N13" s="45" t="n"/>
@@ -18038,8 +18102,8 @@
         </is>
       </c>
       <c r="I14" s="372" t="n"/>
-      <c r="J14" s="255" t="n"/>
-      <c r="K14" s="255" t="n"/>
+      <c r="J14" s="244" t="n"/>
+      <c r="K14" s="244" t="n"/>
       <c r="L14" s="61" t="n"/>
       <c r="M14" s="61" t="n"/>
       <c r="N14" s="61" t="n"/>
@@ -18197,7 +18261,7 @@
           <t>MONTH TO GO</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n"/>
+      <c r="B18" s="245" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="H18" s="98" t="inlineStr">
         <is>
@@ -18209,8 +18273,8 @@
           <t>9-530</t>
         </is>
       </c>
-      <c r="J18" s="210" t="n"/>
-      <c r="K18" s="210" t="inlineStr">
+      <c r="J18" s="209" t="n"/>
+      <c r="K18" s="209" t="inlineStr">
         <is>
           <t>OFFICE</t>
         </is>
@@ -18257,9 +18321,9 @@
       <c r="W18" s="89" t="n"/>
       <c r="X18" s="56" t="n"/>
     </row>
-    <row r="19" hidden="1" ht="17.25" customHeight="1">
+    <row r="19" hidden="1" ht="18.75" customHeight="1">
       <c r="A19" s="94" t="n"/>
-      <c r="B19" s="257">
+      <c r="B19" s="246">
         <f>B15+B18</f>
         <v/>
       </c>
@@ -18279,7 +18343,7 @@
         </is>
       </c>
       <c r="J19" s="129" t="n"/>
-      <c r="K19" s="215" t="n"/>
+      <c r="K19" s="211" t="n"/>
       <c r="L19" s="45" t="n"/>
       <c r="M19" s="45" t="n"/>
       <c r="N19" s="45" t="n"/>
@@ -18294,7 +18358,7 @@
       <c r="W19" s="89" t="n"/>
       <c r="X19" s="56" t="n"/>
     </row>
-    <row r="20" hidden="1" ht="17.25" customHeight="1">
+    <row r="20" hidden="1" ht="18.75" customHeight="1">
       <c r="A20" s="100" t="n"/>
       <c r="B20" s="101" t="n">
         <v>1</v>
@@ -18315,7 +18379,7 @@
         </is>
       </c>
       <c r="J20" s="129" t="n"/>
-      <c r="K20" s="215" t="n"/>
+      <c r="K20" s="211" t="n"/>
       <c r="L20" s="45" t="n"/>
       <c r="M20" s="45" t="n"/>
       <c r="N20" s="45" t="n"/>
@@ -18348,8 +18412,8 @@
           <t>9-1:45</t>
         </is>
       </c>
-      <c r="J21" s="210" t="n"/>
-      <c r="K21" s="210" t="inlineStr">
+      <c r="J21" s="209" t="n"/>
+      <c r="K21" s="209" t="inlineStr">
         <is>
           <t>TASK</t>
         </is>
@@ -18391,7 +18455,7 @@
         </is>
       </c>
       <c r="J22" s="129" t="n"/>
-      <c r="K22" s="210" t="n"/>
+      <c r="K22" s="209" t="n"/>
       <c r="L22" s="180" t="inlineStr">
         <is>
           <t>WOMENS</t>
@@ -18422,7 +18486,7 @@
           <t>MENS</t>
         </is>
       </c>
-      <c r="R22" s="258" t="inlineStr">
+      <c r="R22" s="247" t="inlineStr">
         <is>
           <t>CEL</t>
         </is>
@@ -18457,7 +18521,7 @@
         </is>
       </c>
       <c r="J23" s="129" t="n"/>
-      <c r="K23" s="215" t="n"/>
+      <c r="K23" s="211" t="n"/>
       <c r="L23" s="45" t="n"/>
       <c r="M23" s="92" t="inlineStr">
         <is>
@@ -18485,8 +18549,8 @@
       <c r="X23" s="56" t="n"/>
     </row>
     <row r="24" ht="27.75" customHeight="1">
-      <c r="A24" s="259" t="n"/>
-      <c r="B24" s="260" t="n"/>
+      <c r="A24" s="248" t="n"/>
+      <c r="B24" s="249" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="96" t="n"/>
       <c r="E24" s="96" t="n"/>
@@ -18503,7 +18567,7 @@
         </is>
       </c>
       <c r="J24" s="129" t="n"/>
-      <c r="K24" s="215" t="n"/>
+      <c r="K24" s="211" t="n"/>
       <c r="L24" s="45" t="n"/>
       <c r="M24" s="45" t="n"/>
       <c r="N24" s="115" t="inlineStr">
@@ -18557,7 +18621,7 @@
         </is>
       </c>
       <c r="J25" s="129" t="n"/>
-      <c r="K25" s="215" t="n"/>
+      <c r="K25" s="211" t="n"/>
       <c r="L25" s="45" t="n"/>
       <c r="M25" s="45" t="n"/>
       <c r="N25" s="45" t="n"/>
@@ -18629,7 +18693,7 @@
         </is>
       </c>
       <c r="J26" s="129" t="n"/>
-      <c r="K26" s="215" t="n"/>
+      <c r="K26" s="211" t="n"/>
       <c r="L26" s="45" t="n"/>
       <c r="M26" s="45" t="n"/>
       <c r="N26" s="45" t="n"/>
@@ -18689,7 +18753,7 @@
         </is>
       </c>
       <c r="J27" s="129" t="n"/>
-      <c r="K27" s="215" t="n"/>
+      <c r="K27" s="211" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="45" t="n"/>
       <c r="N27" s="45" t="n"/>
@@ -18733,7 +18797,7 @@
         </is>
       </c>
       <c r="J28" s="129" t="n"/>
-      <c r="K28" s="215" t="n"/>
+      <c r="K28" s="211" t="n"/>
       <c r="L28" s="45" t="n"/>
       <c r="M28" s="45" t="n"/>
       <c r="N28" s="45" t="n"/>
@@ -18756,8 +18820,8 @@
       </c>
     </row>
     <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="261" t="n"/>
-      <c r="B29" s="262" t="n"/>
+      <c r="A29" s="250" t="n"/>
+      <c r="B29" s="251" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="96" t="n"/>
       <c r="E29" s="96" t="n"/>
@@ -18774,7 +18838,7 @@
         </is>
       </c>
       <c r="J29" s="129" t="n"/>
-      <c r="K29" s="215" t="n"/>
+      <c r="K29" s="211" t="n"/>
       <c r="L29" s="45" t="n"/>
       <c r="M29" s="45" t="n"/>
       <c r="N29" s="45" t="n"/>
@@ -18826,7 +18890,7 @@
         </is>
       </c>
       <c r="J30" s="129" t="n"/>
-      <c r="K30" s="215" t="n"/>
+      <c r="K30" s="211" t="n"/>
       <c r="L30" s="45" t="n"/>
       <c r="M30" s="45" t="n"/>
       <c r="N30" s="45" t="n"/>
@@ -18838,10 +18902,10 @@
           <t>SHIPMENT</t>
         </is>
       </c>
-      <c r="S30" s="241" t="n"/>
-      <c r="T30" s="241" t="n"/>
-      <c r="U30" s="241" t="n"/>
-      <c r="V30" s="241" t="n"/>
+      <c r="S30" s="231" t="n"/>
+      <c r="T30" s="231" t="n"/>
+      <c r="U30" s="231" t="n"/>
+      <c r="V30" s="231" t="n"/>
       <c r="W30" s="89" t="n"/>
       <c r="X30" s="127">
         <f>COUNTIF(L32:V32,$R$51)+COUNTIF(L32:V32,$S$51)+COUNTIF(L32:V32,$M$51)+COUNTIF(L32:V32,$N$51)+COUNTIF(L32:V32,$O$51)+COUNTIF(L32:V32,$P$51)+COUNTIF(L32:V32,$Q$51)</f>
@@ -18870,7 +18934,7 @@
         </is>
       </c>
       <c r="J31" s="129" t="n"/>
-      <c r="K31" s="215" t="n"/>
+      <c r="K31" s="211" t="n"/>
       <c r="L31" s="45" t="n"/>
       <c r="M31" s="45" t="n"/>
       <c r="N31" s="45" t="n"/>
@@ -18882,10 +18946,10 @@
           <t>SHIPMENT</t>
         </is>
       </c>
-      <c r="S31" s="241" t="n"/>
-      <c r="T31" s="241" t="n"/>
-      <c r="U31" s="241" t="n"/>
-      <c r="V31" s="241" t="n"/>
+      <c r="S31" s="231" t="n"/>
+      <c r="T31" s="231" t="n"/>
+      <c r="U31" s="231" t="n"/>
+      <c r="V31" s="231" t="n"/>
       <c r="W31" s="89" t="n"/>
       <c r="X31" s="127">
         <f>COUNTIF(#REF!,$R$51)+COUNTIF(#REF!,$S$51)+COUNTIF(#REF!,$M$51)+COUNTIF(#REF!,$N$51)+COUNTIF(#REF!,$O$51)+COUNTIF(#REF!,$P$51)+COUNTIF(#REF!,$Q$51)</f>
@@ -18953,7 +19017,7 @@
       </c>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="263" t="inlineStr">
+      <c r="A34" s="252" t="inlineStr">
         <is>
           <t>BRAND ENVIRONMENT</t>
         </is>
@@ -19041,7 +19105,7 @@
       </c>
     </row>
     <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="263" t="inlineStr">
+      <c r="A37" s="252" t="inlineStr">
         <is>
           <t>HEALTHY &amp; SAFETY</t>
         </is>
@@ -19129,7 +19193,7 @@
       </c>
     </row>
     <row r="40" ht="27.75" customHeight="1">
-      <c r="A40" s="263" t="inlineStr">
+      <c r="A40" s="252" t="inlineStr">
         <is>
           <t>LOSS PREVENTION</t>
         </is>
@@ -19217,7 +19281,7 @@
       </c>
     </row>
     <row r="43" ht="27.75" customHeight="1">
-      <c r="A43" s="263" t="inlineStr">
+      <c r="A43" s="252" t="inlineStr">
         <is>
           <t>MARKETING</t>
         </is>
@@ -19296,7 +19360,7 @@
       <c r="X45" s="134" t="n"/>
     </row>
     <row r="46" ht="27.75" customHeight="1">
-      <c r="A46" s="263" t="inlineStr">
+      <c r="A46" s="252" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
@@ -19350,7 +19414,7 @@
       <c r="X47" s="134" t="n"/>
     </row>
     <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="264" t="n"/>
+      <c r="A48" s="253" t="n"/>
       <c r="B48" s="375" t="n"/>
       <c r="C48" s="124" t="n"/>
       <c r="D48" s="96" t="n"/>
@@ -19501,7 +19565,7 @@
       <c r="W51" s="151" t="n"/>
       <c r="X51" s="134" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="17.25" customHeight="1">
+    <row r="52" hidden="1" ht="18.75" customHeight="1">
       <c r="A52" s="159" t="n"/>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="124" t="n"/>
@@ -19612,7 +19676,7 @@
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="21" max="21"/>
     <col width="15.57642857142857" bestFit="1" customWidth="1" style="160" min="22" max="22"/>
     <col width="34.86214285714286" bestFit="1" customWidth="1" style="166" min="23" max="23"/>
-    <col hidden="1" width="12.43357142857143" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
+    <col hidden="1" width="13.57642857142857" bestFit="1" customWidth="1" style="167" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="88.5" customHeight="1">
@@ -20372,22 +20436,22 @@
       </c>
       <c r="B18" s="208" t="n"/>
       <c r="C18" s="3" t="n"/>
-      <c r="H18" s="209" t="inlineStr"/>
-      <c r="I18" s="209" t="inlineStr"/>
-      <c r="J18" s="210" t="n"/>
-      <c r="K18" s="211" t="inlineStr"/>
-      <c r="L18" s="212" t="inlineStr"/>
-      <c r="M18" s="213" t="inlineStr"/>
-      <c r="N18" s="213" t="inlineStr"/>
-      <c r="O18" s="213" t="inlineStr"/>
-      <c r="P18" s="213" t="inlineStr"/>
-      <c r="Q18" s="213" t="inlineStr"/>
-      <c r="R18" s="213" t="inlineStr"/>
+      <c r="H18" s="99" t="n"/>
+      <c r="I18" s="99" t="n"/>
+      <c r="J18" s="209" t="n"/>
+      <c r="K18" s="209" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="179" t="n"/>
+      <c r="N18" s="179" t="n"/>
+      <c r="O18" s="179" t="n"/>
+      <c r="P18" s="179" t="n"/>
+      <c r="Q18" s="179" t="n"/>
+      <c r="R18" s="179" t="n"/>
       <c r="S18" s="45" t="n"/>
       <c r="T18" s="45" t="n"/>
       <c r="U18" s="45" t="n"/>
       <c r="V18" s="45" t="n"/>
-      <c r="W18" s="214" t="n"/>
+      <c r="W18" s="210" t="n"/>
       <c r="X18" s="56" t="n"/>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -20404,7 +20468,7 @@
       <c r="H19" s="99" t="n"/>
       <c r="I19" s="129" t="n"/>
       <c r="J19" s="129" t="n"/>
-      <c r="K19" s="215" t="n"/>
+      <c r="K19" s="211" t="n"/>
       <c r="L19" s="45" t="n"/>
       <c r="M19" s="45" t="n"/>
       <c r="N19" s="45" t="n"/>
@@ -20416,7 +20480,7 @@
       <c r="T19" s="45" t="n"/>
       <c r="U19" s="45" t="n"/>
       <c r="V19" s="45" t="n"/>
-      <c r="W19" s="214" t="n"/>
+      <c r="W19" s="210" t="n"/>
       <c r="X19" s="56" t="n"/>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -20432,7 +20496,7 @@
       <c r="H20" s="99" t="n"/>
       <c r="I20" s="129" t="n"/>
       <c r="J20" s="129" t="n"/>
-      <c r="K20" s="215" t="n"/>
+      <c r="K20" s="211" t="n"/>
       <c r="L20" s="45" t="n"/>
       <c r="M20" s="45" t="n"/>
       <c r="N20" s="45" t="n"/>
@@ -20444,7 +20508,7 @@
       <c r="T20" s="45" t="n"/>
       <c r="U20" s="45" t="n"/>
       <c r="V20" s="45" t="n"/>
-      <c r="W20" s="214" t="n"/>
+      <c r="W20" s="210" t="n"/>
       <c r="X20" s="56" t="n"/>
     </row>
     <row r="21" ht="27.75" customHeight="1">
@@ -20458,22 +20522,22 @@
       <c r="E21" s="96" t="n"/>
       <c r="F21" s="96" t="n"/>
       <c r="G21" s="97" t="n"/>
-      <c r="H21" s="209" t="inlineStr"/>
-      <c r="I21" s="209" t="inlineStr"/>
+      <c r="H21" s="99" t="n"/>
+      <c r="I21" s="99" t="n"/>
       <c r="J21" s="129" t="n"/>
-      <c r="K21" s="210" t="n"/>
-      <c r="L21" s="213" t="inlineStr"/>
-      <c r="M21" s="216" t="inlineStr"/>
-      <c r="N21" s="216" t="inlineStr"/>
-      <c r="O21" s="216" t="inlineStr"/>
-      <c r="P21" s="216" t="inlineStr"/>
-      <c r="Q21" s="216" t="inlineStr"/>
-      <c r="R21" s="216" t="inlineStr"/>
-      <c r="S21" s="216" t="inlineStr"/>
+      <c r="K21" s="209" t="n"/>
+      <c r="L21" s="179" t="n"/>
+      <c r="M21" s="212" t="n"/>
+      <c r="N21" s="212" t="n"/>
+      <c r="O21" s="212" t="n"/>
+      <c r="P21" s="212" t="n"/>
+      <c r="Q21" s="212" t="n"/>
+      <c r="R21" s="212" t="n"/>
+      <c r="S21" s="212" t="n"/>
       <c r="T21" s="45" t="n"/>
       <c r="U21" s="45" t="n"/>
       <c r="V21" s="45" t="n"/>
-      <c r="W21" s="214" t="n"/>
+      <c r="W21" s="210" t="n"/>
       <c r="X21" s="56" t="n"/>
     </row>
     <row r="22" ht="27.75" customHeight="1">
@@ -20487,11 +20551,11 @@
       <c r="E22" s="96" t="n"/>
       <c r="F22" s="96" t="n"/>
       <c r="G22" s="97" t="n"/>
-      <c r="H22" s="209" t="inlineStr"/>
-      <c r="I22" s="209" t="inlineStr"/>
+      <c r="H22" s="99" t="n"/>
+      <c r="I22" s="99" t="n"/>
       <c r="J22" s="129" t="n"/>
-      <c r="K22" s="210" t="n"/>
-      <c r="L22" s="213" t="inlineStr"/>
+      <c r="K22" s="209" t="n"/>
+      <c r="L22" s="179" t="n"/>
       <c r="M22" s="104" t="n"/>
       <c r="N22" s="104" t="n"/>
       <c r="O22" s="104" t="n"/>
@@ -20502,11 +20566,11 @@
       <c r="T22" s="45" t="n"/>
       <c r="U22" s="45" t="n"/>
       <c r="V22" s="45" t="n"/>
-      <c r="W22" s="214" t="n"/>
+      <c r="W22" s="210" t="n"/>
       <c r="X22" s="56" t="n"/>
     </row>
     <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="217" t="inlineStr">
+      <c r="A23" s="213" t="inlineStr">
         <is>
           <t>SW. $34.99, $39.99, 44.99, 49.99</t>
         </is>
@@ -20517,22 +20581,22 @@
       <c r="E23" s="96" t="n"/>
       <c r="F23" s="96" t="n"/>
       <c r="G23" s="97" t="n"/>
-      <c r="H23" s="209" t="inlineStr"/>
-      <c r="I23" s="209" t="inlineStr"/>
+      <c r="H23" s="99" t="n"/>
+      <c r="I23" s="99" t="n"/>
       <c r="J23" s="129" t="n"/>
-      <c r="K23" s="215" t="n"/>
+      <c r="K23" s="211" t="n"/>
       <c r="L23" s="45" t="n"/>
-      <c r="M23" s="212" t="inlineStr"/>
-      <c r="N23" s="218" t="inlineStr"/>
-      <c r="O23" s="218" t="inlineStr"/>
-      <c r="P23" s="218" t="inlineStr"/>
-      <c r="Q23" s="218" t="inlineStr"/>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="92" t="n"/>
+      <c r="O23" s="92" t="n"/>
+      <c r="P23" s="92" t="n"/>
+      <c r="Q23" s="92" t="n"/>
       <c r="R23" s="45" t="n"/>
       <c r="S23" s="45" t="n"/>
       <c r="T23" s="45" t="n"/>
       <c r="U23" s="45" t="n"/>
       <c r="V23" s="45" t="n"/>
-      <c r="W23" s="219" t="n"/>
+      <c r="W23" s="214" t="n"/>
       <c r="X23" s="127" t="n"/>
     </row>
     <row r="24" ht="27.75" customHeight="1">
@@ -20546,100 +20610,100 @@
       <c r="E24" s="96" t="n"/>
       <c r="F24" s="96" t="n"/>
       <c r="G24" s="97" t="n"/>
-      <c r="H24" s="209" t="inlineStr"/>
-      <c r="I24" s="209" t="inlineStr"/>
+      <c r="H24" s="99" t="n"/>
+      <c r="I24" s="99" t="n"/>
       <c r="J24" s="129" t="n"/>
-      <c r="K24" s="215" t="n"/>
+      <c r="K24" s="211" t="n"/>
       <c r="L24" s="45" t="n"/>
       <c r="M24" s="45" t="n"/>
-      <c r="N24" s="212" t="inlineStr"/>
-      <c r="O24" s="220" t="inlineStr"/>
-      <c r="P24" s="220" t="inlineStr"/>
-      <c r="Q24" s="220" t="inlineStr"/>
-      <c r="R24" s="220" t="inlineStr"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="115" t="n"/>
+      <c r="P24" s="115" t="n"/>
+      <c r="Q24" s="115" t="n"/>
+      <c r="R24" s="115" t="n"/>
       <c r="S24" s="45" t="n"/>
       <c r="T24" s="45" t="n"/>
       <c r="U24" s="45" t="n"/>
       <c r="V24" s="45" t="n"/>
-      <c r="W24" s="219" t="n"/>
+      <c r="W24" s="214" t="n"/>
       <c r="X24" s="127" t="n"/>
     </row>
     <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="221" t="n"/>
+      <c r="A25" s="215" t="n"/>
       <c r="B25" s="113" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="96" t="n"/>
       <c r="E25" s="96" t="n"/>
-      <c r="F25" s="222" t="n"/>
-      <c r="G25" s="223" t="n"/>
-      <c r="H25" s="209" t="inlineStr"/>
-      <c r="I25" s="209" t="inlineStr"/>
+      <c r="F25" s="216" t="n"/>
+      <c r="G25" s="217" t="n"/>
+      <c r="H25" s="99" t="n"/>
+      <c r="I25" s="99" t="n"/>
       <c r="J25" s="129" t="n"/>
-      <c r="K25" s="215" t="n"/>
+      <c r="K25" s="211" t="n"/>
       <c r="L25" s="45" t="n"/>
       <c r="M25" s="45" t="n"/>
-      <c r="N25" s="212" t="inlineStr"/>
+      <c r="N25" s="49" t="n"/>
       <c r="O25" s="105" t="n"/>
-      <c r="P25" s="224" t="inlineStr"/>
-      <c r="Q25" s="220" t="inlineStr"/>
-      <c r="R25" s="220" t="inlineStr"/>
+      <c r="P25" s="109" t="n"/>
+      <c r="Q25" s="115" t="n"/>
+      <c r="R25" s="115" t="n"/>
       <c r="S25" s="45" t="n"/>
       <c r="T25" s="45" t="n"/>
       <c r="U25" s="45" t="n"/>
       <c r="V25" s="45" t="n"/>
-      <c r="W25" s="225" t="n"/>
-      <c r="X25" s="226" t="n"/>
+      <c r="W25" s="218" t="n"/>
+      <c r="X25" s="219" t="n"/>
     </row>
     <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="227" t="n"/>
+      <c r="A26" s="220" t="n"/>
       <c r="B26" s="118" t="n"/>
-      <c r="C26" s="228" t="n"/>
+      <c r="C26" s="221" t="n"/>
       <c r="D26" s="96" t="n"/>
       <c r="E26" s="96" t="n"/>
-      <c r="F26" s="222" t="n"/>
-      <c r="G26" s="229" t="n"/>
-      <c r="H26" s="230" t="inlineStr"/>
-      <c r="I26" s="211" t="inlineStr"/>
-      <c r="J26" s="215" t="n"/>
-      <c r="K26" s="210" t="n"/>
+      <c r="F26" s="216" t="n"/>
+      <c r="G26" s="222" t="n"/>
+      <c r="H26" s="130" t="n"/>
+      <c r="I26" s="209" t="n"/>
+      <c r="J26" s="211" t="n"/>
+      <c r="K26" s="209" t="n"/>
       <c r="L26" s="45" t="n"/>
       <c r="M26" s="45" t="n"/>
       <c r="N26" s="45" t="n"/>
-      <c r="O26" s="220" t="inlineStr"/>
-      <c r="P26" s="220" t="inlineStr"/>
-      <c r="Q26" s="220" t="inlineStr"/>
-      <c r="R26" s="220" t="inlineStr"/>
-      <c r="S26" s="212" t="inlineStr"/>
-      <c r="T26" s="231" t="inlineStr"/>
-      <c r="U26" s="231" t="inlineStr"/>
-      <c r="V26" s="231" t="inlineStr"/>
-      <c r="W26" s="232" t="n"/>
+      <c r="O26" s="115" t="n"/>
+      <c r="P26" s="115" t="n"/>
+      <c r="Q26" s="115" t="n"/>
+      <c r="R26" s="115" t="n"/>
+      <c r="S26" s="49" t="n"/>
+      <c r="T26" s="86" t="n"/>
+      <c r="U26" s="86" t="n"/>
+      <c r="V26" s="86" t="n"/>
+      <c r="W26" s="223" t="n"/>
       <c r="X26" s="29" t="n"/>
     </row>
     <row r="27" ht="23.25" customHeight="1">
-      <c r="A27" s="227" t="n"/>
+      <c r="A27" s="220" t="n"/>
       <c r="B27" s="118" t="n"/>
-      <c r="C27" s="233" t="n"/>
+      <c r="C27" s="224" t="n"/>
       <c r="D27" s="96" t="n"/>
       <c r="E27" s="97" t="n"/>
       <c r="F27" s="96" t="n"/>
-      <c r="G27" s="234" t="n"/>
-      <c r="H27" s="230" t="inlineStr"/>
-      <c r="I27" s="211" t="inlineStr"/>
-      <c r="J27" s="215" t="n"/>
-      <c r="K27" s="210" t="n"/>
+      <c r="G27" s="225" t="n"/>
+      <c r="H27" s="130" t="n"/>
+      <c r="I27" s="209" t="n"/>
+      <c r="J27" s="211" t="n"/>
+      <c r="K27" s="209" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="45" t="n"/>
       <c r="N27" s="45" t="n"/>
       <c r="O27" s="45" t="n"/>
-      <c r="P27" s="220" t="inlineStr"/>
-      <c r="Q27" s="220" t="inlineStr"/>
-      <c r="R27" s="220" t="inlineStr"/>
-      <c r="S27" s="212" t="inlineStr"/>
-      <c r="T27" s="231" t="inlineStr"/>
+      <c r="P27" s="115" t="n"/>
+      <c r="Q27" s="115" t="n"/>
+      <c r="R27" s="115" t="n"/>
+      <c r="S27" s="49" t="n"/>
+      <c r="T27" s="86" t="n"/>
       <c r="U27" s="45" t="n"/>
-      <c r="V27" s="235" t="n"/>
-      <c r="W27" s="214" t="n"/>
+      <c r="V27" s="226" t="n"/>
+      <c r="W27" s="210" t="n"/>
       <c r="X27" s="29" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -20647,24 +20711,24 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="96" t="n"/>
       <c r="E28" s="96" t="n"/>
-      <c r="F28" s="236" t="n"/>
-      <c r="G28" s="237" t="n"/>
-      <c r="H28" s="209" t="inlineStr"/>
-      <c r="I28" s="209" t="inlineStr"/>
+      <c r="F28" s="227" t="n"/>
+      <c r="G28" s="228" t="n"/>
+      <c r="H28" s="99" t="n"/>
+      <c r="I28" s="99" t="n"/>
       <c r="J28" s="129" t="n"/>
-      <c r="K28" s="215" t="n"/>
+      <c r="K28" s="211" t="n"/>
       <c r="L28" s="45" t="n"/>
       <c r="M28" s="45" t="n"/>
       <c r="N28" s="45" t="n"/>
       <c r="O28" s="45" t="n"/>
       <c r="P28" s="45" t="n"/>
-      <c r="Q28" s="238" t="n"/>
-      <c r="R28" s="239" t="inlineStr"/>
+      <c r="Q28" s="229" t="n"/>
+      <c r="R28" s="91" t="n"/>
       <c r="S28" s="108" t="n"/>
       <c r="T28" s="108" t="n"/>
       <c r="U28" s="108" t="n"/>
       <c r="V28" s="108" t="n"/>
-      <c r="W28" s="240" t="inlineStr">
+      <c r="W28" s="230" t="inlineStr">
         <is>
           <t>PRE-CLOSE</t>
         </is>
@@ -20679,22 +20743,22 @@
       <c r="E29" s="96" t="n"/>
       <c r="F29" s="96" t="n"/>
       <c r="G29" s="97" t="n"/>
-      <c r="H29" s="209" t="inlineStr"/>
-      <c r="I29" s="209" t="inlineStr"/>
+      <c r="H29" s="99" t="n"/>
+      <c r="I29" s="99" t="n"/>
       <c r="J29" s="129" t="n"/>
-      <c r="K29" s="215" t="n"/>
+      <c r="K29" s="211" t="n"/>
       <c r="L29" s="45" t="n"/>
       <c r="M29" s="45" t="n"/>
       <c r="N29" s="45" t="n"/>
       <c r="O29" s="45" t="n"/>
       <c r="P29" s="45" t="n"/>
       <c r="Q29" s="45" t="n"/>
-      <c r="R29" s="213" t="inlineStr"/>
+      <c r="R29" s="179" t="n"/>
       <c r="S29" s="93" t="n"/>
       <c r="T29" s="93" t="n"/>
       <c r="U29" s="93" t="n"/>
       <c r="V29" s="93" t="n"/>
-      <c r="W29" s="214" t="n"/>
+      <c r="W29" s="210" t="n"/>
       <c r="X29" s="127" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -20704,22 +20768,22 @@
       <c r="E30" s="96" t="n"/>
       <c r="F30" s="96" t="n"/>
       <c r="G30" s="97" t="n"/>
-      <c r="H30" s="209" t="inlineStr"/>
-      <c r="I30" s="209" t="inlineStr"/>
+      <c r="H30" s="99" t="n"/>
+      <c r="I30" s="99" t="n"/>
       <c r="J30" s="129" t="n"/>
-      <c r="K30" s="215" t="n"/>
+      <c r="K30" s="211" t="n"/>
       <c r="L30" s="45" t="n"/>
       <c r="M30" s="45" t="n"/>
       <c r="N30" s="45" t="n"/>
       <c r="O30" s="45" t="n"/>
       <c r="P30" s="45" t="n"/>
       <c r="Q30" s="45" t="n"/>
-      <c r="R30" s="212" t="inlineStr"/>
+      <c r="R30" s="49" t="n"/>
       <c r="S30" s="105" t="n"/>
       <c r="T30" s="105" t="n"/>
       <c r="U30" s="105" t="n"/>
       <c r="V30" s="105" t="n"/>
-      <c r="W30" s="214" t="n"/>
+      <c r="W30" s="210" t="n"/>
       <c r="X30" s="127" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -20730,22 +20794,22 @@
       <c r="E31" s="96" t="n"/>
       <c r="F31" s="96" t="n"/>
       <c r="G31" s="97" t="n"/>
-      <c r="H31" s="209" t="inlineStr"/>
-      <c r="I31" s="209" t="inlineStr"/>
+      <c r="H31" s="99" t="n"/>
+      <c r="I31" s="99" t="n"/>
       <c r="J31" s="129" t="n"/>
-      <c r="K31" s="215" t="n"/>
+      <c r="K31" s="211" t="n"/>
       <c r="L31" s="45" t="n"/>
       <c r="M31" s="45" t="n"/>
       <c r="N31" s="45" t="n"/>
       <c r="O31" s="45" t="n"/>
       <c r="P31" s="45" t="n"/>
       <c r="Q31" s="45" t="n"/>
-      <c r="R31" s="212" t="inlineStr"/>
+      <c r="R31" s="49" t="n"/>
       <c r="S31" s="104" t="n"/>
       <c r="T31" s="104" t="n"/>
       <c r="U31" s="104" t="n"/>
       <c r="V31" s="104" t="n"/>
-      <c r="W31" s="214" t="n"/>
+      <c r="W31" s="210" t="n"/>
       <c r="X31" s="127" t="n"/>
     </row>
     <row r="32" ht="22.5" customHeight="1">
@@ -20760,22 +20824,22 @@
       <c r="E32" s="96" t="n"/>
       <c r="F32" s="96" t="n"/>
       <c r="G32" s="97" t="n"/>
-      <c r="H32" s="209" t="inlineStr"/>
-      <c r="I32" s="209" t="inlineStr"/>
+      <c r="H32" s="99" t="n"/>
+      <c r="I32" s="99" t="n"/>
       <c r="J32" s="129" t="n"/>
-      <c r="K32" s="215" t="n"/>
+      <c r="K32" s="211" t="n"/>
       <c r="L32" s="45" t="n"/>
       <c r="M32" s="45" t="n"/>
       <c r="N32" s="45" t="n"/>
       <c r="O32" s="45" t="n"/>
       <c r="P32" s="45" t="n"/>
       <c r="Q32" s="45" t="n"/>
-      <c r="R32" s="212" t="inlineStr"/>
-      <c r="S32" s="241" t="n"/>
-      <c r="T32" s="241" t="n"/>
-      <c r="U32" s="241" t="n"/>
-      <c r="V32" s="241" t="n"/>
-      <c r="W32" s="214" t="n"/>
+      <c r="R32" s="49" t="n"/>
+      <c r="S32" s="231" t="n"/>
+      <c r="T32" s="231" t="n"/>
+      <c r="U32" s="231" t="n"/>
+      <c r="V32" s="231" t="n"/>
+      <c r="W32" s="210" t="n"/>
       <c r="X32" s="127">
         <f>COUNTIF(#REF!,$R$48)+COUNTIF(#REF!,$S$48)+COUNTIF(#REF!,$M$48)+COUNTIF(#REF!,$N$48)+COUNTIF(#REF!,$O$48)+COUNTIF(#REF!,$P$48)+COUNTIF(#REF!,$Q$48)</f>
         <v/>
@@ -20789,8 +20853,8 @@
       <c r="E33" s="96" t="n"/>
       <c r="F33" s="96" t="n"/>
       <c r="G33" s="97" t="n"/>
-      <c r="H33" s="209" t="inlineStr"/>
-      <c r="I33" s="209" t="inlineStr"/>
+      <c r="H33" s="99" t="n"/>
+      <c r="I33" s="99" t="n"/>
       <c r="J33" s="129" t="n"/>
       <c r="K33" s="129" t="n"/>
       <c r="L33" s="119" t="n"/>
@@ -20798,13 +20862,13 @@
       <c r="N33" s="119" t="n"/>
       <c r="O33" s="119" t="n"/>
       <c r="P33" s="119" t="n"/>
-      <c r="Q33" s="242" t="n"/>
-      <c r="R33" s="243" t="inlineStr"/>
-      <c r="S33" s="244" t="n"/>
-      <c r="T33" s="244" t="n"/>
-      <c r="U33" s="241" t="n"/>
-      <c r="V33" s="241" t="n"/>
-      <c r="W33" s="214" t="n"/>
+      <c r="Q33" s="232" t="n"/>
+      <c r="R33" s="180" t="n"/>
+      <c r="S33" s="233" t="n"/>
+      <c r="T33" s="233" t="n"/>
+      <c r="U33" s="231" t="n"/>
+      <c r="V33" s="231" t="n"/>
+      <c r="W33" s="210" t="n"/>
       <c r="X33" s="127">
         <f>COUNTIF(L33:V33,$R$48)+COUNTIF(L33:V33,$S$48)+COUNTIF(L33:V33,$M$48)+COUNTIF(L33:V33,$N$48)+COUNTIF(L33:V33,$O$48)+COUNTIF(L33:V33,$P$48)+COUNTIF(L33:V33,$Q$48)</f>
         <v/>
@@ -20822,22 +20886,22 @@
       <c r="E34" s="96" t="n"/>
       <c r="F34" s="96" t="n"/>
       <c r="G34" s="97" t="n"/>
-      <c r="H34" s="209" t="inlineStr"/>
-      <c r="I34" s="209" t="inlineStr"/>
-      <c r="J34" s="215" t="n"/>
-      <c r="K34" s="245" t="inlineStr"/>
-      <c r="L34" s="246" t="n"/>
-      <c r="M34" s="246" t="n"/>
-      <c r="N34" s="246" t="n"/>
-      <c r="O34" s="246" t="n"/>
-      <c r="P34" s="247" t="n"/>
+      <c r="H34" s="99" t="n"/>
+      <c r="I34" s="99" t="n"/>
+      <c r="J34" s="211" t="n"/>
+      <c r="K34" s="234" t="n"/>
+      <c r="L34" s="235" t="n"/>
+      <c r="M34" s="235" t="n"/>
+      <c r="N34" s="235" t="n"/>
+      <c r="O34" s="235" t="n"/>
+      <c r="P34" s="236" t="n"/>
       <c r="Q34" s="119" t="n"/>
       <c r="R34" s="119" t="n"/>
       <c r="S34" s="119" t="n"/>
       <c r="T34" s="119" t="n"/>
       <c r="U34" s="119" t="n"/>
       <c r="V34" s="119" t="n"/>
-      <c r="W34" s="214" t="n"/>
+      <c r="W34" s="210" t="n"/>
       <c r="X34" s="127">
         <f>COUNTIF(L34:V34,$R$48)+COUNTIF(L34:V34,$S$48)+COUNTIF(L34:V34,$M$48)+COUNTIF(L34:V34,$N$48)+COUNTIF(L34:V34,$O$48)+COUNTIF(L34:V34,$P$48)+COUNTIF(L34:V34,$Q$48)</f>
         <v/>
@@ -20870,7 +20934,7 @@
       <c r="T35" s="119" t="n"/>
       <c r="U35" s="119" t="n"/>
       <c r="V35" s="119" t="n"/>
-      <c r="W35" s="214" t="n"/>
+      <c r="W35" s="210" t="n"/>
       <c r="X35" s="127">
         <f>COUNTIF(L35:V35,$R$48)+COUNTIF(L35:V35,$S$48)+COUNTIF(L35:V35,$M$48)+COUNTIF(L35:V35,$N$48)+COUNTIF(L35:V35,$O$48)+COUNTIF(L35:V35,$P$48)+COUNTIF(L35:V35,$Q$48)</f>
         <v/>
@@ -20899,7 +20963,7 @@
       <c r="T36" s="119" t="n"/>
       <c r="U36" s="119" t="n"/>
       <c r="V36" s="119" t="n"/>
-      <c r="W36" s="214" t="n"/>
+      <c r="W36" s="210" t="n"/>
       <c r="X36" s="127">
         <f>COUNTIF(L36:V36,$R$48)+COUNTIF(L36:V36,$S$48)+COUNTIF(L36:V36,$M$48)+COUNTIF(L36:V36,$N$48)+COUNTIF(L36:V36,$O$48)+COUNTIF(L36:V36,$P$48)+COUNTIF(L36:V36,$Q$48)</f>
         <v/>
@@ -21103,8 +21167,8 @@
       <c r="G43" s="97" t="n"/>
       <c r="H43" s="132" t="n"/>
       <c r="I43" s="136" t="n"/>
-      <c r="J43" s="248" t="n"/>
-      <c r="K43" s="248" t="n"/>
+      <c r="J43" s="237" t="n"/>
+      <c r="K43" s="237" t="n"/>
       <c r="L43" s="119" t="n"/>
       <c r="M43" s="119" t="n"/>
       <c r="N43" s="119" t="n"/>
